--- a/grupos/1DM - Estadisticos 20231.xlsx
+++ b/grupos/1DM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="127">
   <si>
     <t>Materia</t>
   </si>
@@ -146,6 +146,9 @@
     <t>RIVERA OLMOS MELANY</t>
   </si>
   <si>
+    <t>RODRIGUEZ GUEVARA ANIELA SAMANTA</t>
+  </si>
+  <si>
     <t>ROMAN TEZOCO CONCEPCION GUADALUPE</t>
   </si>
   <si>
@@ -224,15 +227,15 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Santiago Hernández Mariana</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Santiago Hernández Mariana</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
@@ -248,6 +251,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>ANIELA SAMANTA</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -303,9 +315,6 @@
   </si>
   <si>
     <t>TZNAHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>OLMOS</t>
@@ -751,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3476,88 +3485,88 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F33">
+        <v>6</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+      <c r="H33">
+        <v>5</v>
+      </c>
+      <c r="I33">
+        <v>-1</v>
+      </c>
+      <c r="J33">
+        <v>-1</v>
+      </c>
+      <c r="K33">
+        <v>-1</v>
+      </c>
+      <c r="L33">
+        <v>-1</v>
+      </c>
+      <c r="M33">
+        <v>-1</v>
+      </c>
+      <c r="N33">
+        <v>-1</v>
+      </c>
+      <c r="O33">
+        <v>-1</v>
+      </c>
+      <c r="P33">
+        <v>-1</v>
+      </c>
+      <c r="Q33">
+        <v>-1</v>
+      </c>
+      <c r="R33">
+        <v>-1</v>
+      </c>
+      <c r="S33">
+        <v>-1</v>
+      </c>
+      <c r="T33">
+        <v>-1</v>
+      </c>
+      <c r="U33">
+        <v>-1</v>
+      </c>
+      <c r="V33">
+        <v>-1</v>
+      </c>
+      <c r="W33">
+        <v>6</v>
+      </c>
+      <c r="X33">
         <v>7</v>
       </c>
-      <c r="G33">
-        <v>10</v>
-      </c>
-      <c r="H33">
-        <v>10</v>
-      </c>
-      <c r="I33">
-        <v>-1</v>
-      </c>
-      <c r="J33">
-        <v>-1</v>
-      </c>
-      <c r="K33">
-        <v>-1</v>
-      </c>
-      <c r="L33">
-        <v>-1</v>
-      </c>
-      <c r="M33">
-        <v>-1</v>
-      </c>
-      <c r="N33">
-        <v>-1</v>
-      </c>
-      <c r="O33">
-        <v>-1</v>
-      </c>
-      <c r="P33">
-        <v>-1</v>
-      </c>
-      <c r="Q33">
-        <v>-1</v>
-      </c>
-      <c r="R33">
-        <v>-1</v>
-      </c>
-      <c r="S33">
-        <v>-1</v>
-      </c>
-      <c r="T33">
-        <v>-1</v>
-      </c>
-      <c r="U33">
-        <v>-1</v>
-      </c>
-      <c r="V33">
-        <v>-1</v>
-      </c>
-      <c r="W33">
-        <v>9</v>
-      </c>
-      <c r="X33">
-        <v>8</v>
-      </c>
       <c r="Y33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3568,22 +3577,22 @@
         <v>9</v>
       </c>
       <c r="C34">
+        <v>8</v>
+      </c>
+      <c r="D34">
+        <v>9</v>
+      </c>
+      <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34">
         <v>7</v>
       </c>
-      <c r="D34">
-        <v>8</v>
-      </c>
-      <c r="E34">
-        <v>9</v>
-      </c>
-      <c r="F34">
-        <v>5</v>
-      </c>
       <c r="G34">
         <v>10</v>
       </c>
       <c r="H34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3631,22 +3640,22 @@
         <v>9</v>
       </c>
       <c r="X34">
+        <v>8</v>
+      </c>
+      <c r="Y34">
+        <v>9</v>
+      </c>
+      <c r="Z34">
+        <v>10</v>
+      </c>
+      <c r="AA34">
         <v>7</v>
       </c>
-      <c r="Y34">
-        <v>8</v>
-      </c>
-      <c r="Z34">
-        <v>9</v>
-      </c>
-      <c r="AA34">
-        <v>5</v>
-      </c>
       <c r="AB34">
         <v>10</v>
       </c>
       <c r="AC34">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3657,22 +3666,22 @@
         <v>9</v>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E35">
         <v>9</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G35">
         <v>10</v>
       </c>
       <c r="H35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3720,22 +3729,22 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z35">
         <v>9</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB35">
         <v>10</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3752,10 +3761,10 @@
         <v>9</v>
       </c>
       <c r="E36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G36">
         <v>10</v>
@@ -3815,10 +3824,10 @@
         <v>9</v>
       </c>
       <c r="Z36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB36">
         <v>10</v>
@@ -3835,17 +3844,17 @@
         <v>9</v>
       </c>
       <c r="C37">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+      <c r="F37">
         <v>7</v>
       </c>
-      <c r="D37">
-        <v>8</v>
-      </c>
-      <c r="E37">
-        <v>9</v>
-      </c>
-      <c r="F37">
-        <v>5</v>
-      </c>
       <c r="G37">
         <v>10</v>
       </c>
@@ -3898,16 +3907,16 @@
         <v>9</v>
       </c>
       <c r="X37">
+        <v>8</v>
+      </c>
+      <c r="Y37">
+        <v>9</v>
+      </c>
+      <c r="Z37">
+        <v>10</v>
+      </c>
+      <c r="AA37">
         <v>7</v>
-      </c>
-      <c r="Y37">
-        <v>8</v>
-      </c>
-      <c r="Z37">
-        <v>9</v>
-      </c>
-      <c r="AA37">
-        <v>5</v>
       </c>
       <c r="AB37">
         <v>10</v>
@@ -3924,85 +3933,85 @@
         <v>9</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E38">
         <v>9</v>
       </c>
       <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>10</v>
+      </c>
+      <c r="H38">
+        <v>10</v>
+      </c>
+      <c r="I38">
+        <v>-1</v>
+      </c>
+      <c r="J38">
+        <v>-1</v>
+      </c>
+      <c r="K38">
+        <v>-1</v>
+      </c>
+      <c r="L38">
+        <v>-1</v>
+      </c>
+      <c r="M38">
+        <v>-1</v>
+      </c>
+      <c r="N38">
+        <v>-1</v>
+      </c>
+      <c r="O38">
+        <v>-1</v>
+      </c>
+      <c r="P38">
+        <v>-1</v>
+      </c>
+      <c r="Q38">
+        <v>-1</v>
+      </c>
+      <c r="R38">
+        <v>-1</v>
+      </c>
+      <c r="S38">
+        <v>-1</v>
+      </c>
+      <c r="T38">
+        <v>-1</v>
+      </c>
+      <c r="U38">
+        <v>-1</v>
+      </c>
+      <c r="V38">
+        <v>-1</v>
+      </c>
+      <c r="W38">
+        <v>9</v>
+      </c>
+      <c r="X38">
         <v>7</v>
       </c>
-      <c r="G38">
-        <v>10</v>
-      </c>
-      <c r="H38">
-        <v>9</v>
-      </c>
-      <c r="I38">
-        <v>-1</v>
-      </c>
-      <c r="J38">
-        <v>-1</v>
-      </c>
-      <c r="K38">
-        <v>-1</v>
-      </c>
-      <c r="L38">
-        <v>-1</v>
-      </c>
-      <c r="M38">
-        <v>-1</v>
-      </c>
-      <c r="N38">
-        <v>-1</v>
-      </c>
-      <c r="O38">
-        <v>-1</v>
-      </c>
-      <c r="P38">
-        <v>-1</v>
-      </c>
-      <c r="Q38">
-        <v>-1</v>
-      </c>
-      <c r="R38">
-        <v>-1</v>
-      </c>
-      <c r="S38">
-        <v>-1</v>
-      </c>
-      <c r="T38">
-        <v>-1</v>
-      </c>
-      <c r="U38">
-        <v>-1</v>
-      </c>
-      <c r="V38">
-        <v>-1</v>
-      </c>
-      <c r="W38">
-        <v>9</v>
-      </c>
-      <c r="X38">
-        <v>6</v>
-      </c>
       <c r="Y38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z38">
         <v>9</v>
       </c>
       <c r="AA38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB38">
         <v>10</v>
       </c>
       <c r="AC38">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -4010,25 +4019,25 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E39">
         <v>9</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G39">
         <v>10</v>
       </c>
       <c r="H39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -4073,25 +4082,25 @@
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z39">
         <v>9</v>
       </c>
       <c r="AA39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB39">
         <v>10</v>
       </c>
       <c r="AC39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -4099,25 +4108,25 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C40">
         <v>5</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F40">
         <v>5</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -4162,25 +4171,25 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>5</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z40">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA40">
         <v>5</v>
       </c>
       <c r="AB40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC40">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4188,25 +4197,25 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H41">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>-1</v>
@@ -4251,25 +4260,25 @@
         <v>-1</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC41">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -4277,7 +4286,7 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C42">
         <v>7</v>
@@ -4289,7 +4298,7 @@
         <v>8</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G42">
         <v>10</v>
@@ -4340,7 +4349,7 @@
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X42">
         <v>7</v>
@@ -4352,12 +4361,101 @@
         <v>8</v>
       </c>
       <c r="AA42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB42">
         <v>10</v>
       </c>
       <c r="AC42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43">
+        <v>8</v>
+      </c>
+      <c r="C43">
+        <v>7</v>
+      </c>
+      <c r="D43">
+        <v>8</v>
+      </c>
+      <c r="E43">
+        <v>8</v>
+      </c>
+      <c r="F43">
+        <v>6</v>
+      </c>
+      <c r="G43">
+        <v>10</v>
+      </c>
+      <c r="H43">
+        <v>9</v>
+      </c>
+      <c r="I43">
+        <v>-1</v>
+      </c>
+      <c r="J43">
+        <v>-1</v>
+      </c>
+      <c r="K43">
+        <v>-1</v>
+      </c>
+      <c r="L43">
+        <v>-1</v>
+      </c>
+      <c r="M43">
+        <v>-1</v>
+      </c>
+      <c r="N43">
+        <v>-1</v>
+      </c>
+      <c r="O43">
+        <v>-1</v>
+      </c>
+      <c r="P43">
+        <v>-1</v>
+      </c>
+      <c r="Q43">
+        <v>-1</v>
+      </c>
+      <c r="R43">
+        <v>-1</v>
+      </c>
+      <c r="S43">
+        <v>-1</v>
+      </c>
+      <c r="T43">
+        <v>-1</v>
+      </c>
+      <c r="U43">
+        <v>-1</v>
+      </c>
+      <c r="V43">
+        <v>-1</v>
+      </c>
+      <c r="W43">
+        <v>8</v>
+      </c>
+      <c r="X43">
+        <v>7</v>
+      </c>
+      <c r="Y43">
+        <v>8</v>
+      </c>
+      <c r="Z43">
+        <v>8</v>
+      </c>
+      <c r="AA43">
+        <v>6</v>
+      </c>
+      <c r="AB43">
+        <v>10</v>
+      </c>
+      <c r="AC43">
         <v>9</v>
       </c>
     </row>
@@ -4374,7 +4472,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -4383,7 +4481,7 @@
     <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4392,7 +4490,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -4401,7 +4499,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -4494,10 +4592,10 @@
         <v>80</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F4">
         <v>80</v>
@@ -4515,10 +4613,10 @@
         <v>80</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M4">
         <v>80</v>
@@ -4536,10 +4634,10 @@
         <v>80</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T4">
         <v>80</v>
@@ -4562,10 +4660,10 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -4583,10 +4681,10 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -4604,10 +4702,10 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -4630,10 +4728,10 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -4651,10 +4749,10 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -4672,10 +4770,10 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T6">
         <v>100</v>
@@ -4698,10 +4796,10 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E7">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="F7">
         <v>85</v>
@@ -4719,10 +4817,10 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L7">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="M7">
         <v>85</v>
@@ -4740,10 +4838,10 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S7">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="T7">
         <v>85</v>
@@ -4766,10 +4864,10 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -4787,10 +4885,10 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -4808,10 +4906,10 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -4834,10 +4932,10 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -4855,10 +4953,10 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -4876,10 +4974,10 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -4902,10 +5000,10 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -4923,10 +5021,10 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -4944,10 +5042,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -4970,10 +5068,10 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -4991,10 +5089,10 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -5012,10 +5110,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -5038,10 +5136,10 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -5059,10 +5157,10 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -5080,10 +5178,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -5106,10 +5204,10 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -5127,10 +5225,10 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -5148,10 +5246,10 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -5174,10 +5272,10 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -5195,10 +5293,10 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -5216,10 +5314,10 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T14">
         <v>100</v>
@@ -5242,10 +5340,10 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -5263,10 +5361,10 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -5284,10 +5382,10 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T15">
         <v>100</v>
@@ -5310,10 +5408,10 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -5331,10 +5429,10 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -5352,10 +5450,10 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -5378,10 +5476,10 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -5399,10 +5497,10 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -5420,10 +5518,10 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -5446,10 +5544,10 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -5467,10 +5565,10 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -5488,10 +5586,10 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -5514,10 +5612,10 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="E19">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -5535,10 +5633,10 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="L19">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -5556,10 +5654,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="S19">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="T19">
         <v>100</v>
@@ -5582,10 +5680,10 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E20">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -5603,10 +5701,10 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L20">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -5624,10 +5722,10 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S20">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -5650,10 +5748,10 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -5671,10 +5769,10 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -5692,10 +5790,10 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -5718,10 +5816,10 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -5739,10 +5837,10 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -5760,10 +5858,10 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -5786,10 +5884,10 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E23">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F23">
         <v>100</v>
@@ -5807,10 +5905,10 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L23">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -5828,10 +5926,10 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S23">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5854,10 +5952,10 @@
         <v>100</v>
       </c>
       <c r="D24">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="E24">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -5875,10 +5973,10 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="L24">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -5896,10 +5994,10 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="S24">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5922,10 +6020,10 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -5943,10 +6041,10 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -5964,10 +6062,10 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -5990,10 +6088,10 @@
         <v>80</v>
       </c>
       <c r="D26">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -6011,10 +6109,10 @@
         <v>80</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -6032,10 +6130,10 @@
         <v>80</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -6058,10 +6156,10 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -6079,10 +6177,10 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -6100,10 +6198,10 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T27">
         <v>100</v>
@@ -6126,10 +6224,10 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -6147,10 +6245,10 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -6168,10 +6266,10 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>90</v>
+        <v>78.3</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T28">
         <v>100</v>
@@ -6194,10 +6292,10 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -6215,10 +6313,10 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -6236,10 +6334,10 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -6262,10 +6360,10 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E30">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -6283,10 +6381,10 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L30">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -6304,10 +6402,10 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S30">
-        <v>93.3</v>
+        <v>87.5</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -6330,10 +6428,10 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E31">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -6351,10 +6449,10 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -6372,10 +6470,10 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -6398,10 +6496,10 @@
         <v>100</v>
       </c>
       <c r="D32">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -6419,10 +6517,10 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M32">
         <v>100</v>
@@ -6440,10 +6538,10 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -6460,7 +6558,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -6475,13 +6573,13 @@
         <v>100</v>
       </c>
       <c r="G33">
-        <v>93.8</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -6496,13 +6594,13 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>93.8</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P33">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -6517,10 +6615,10 @@
         <v>100</v>
       </c>
       <c r="U33">
-        <v>93.8</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6534,16 +6632,16 @@
         <v>100</v>
       </c>
       <c r="D34">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E34">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F34">
         <v>100</v>
       </c>
       <c r="G34">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="H34">
         <v>100</v>
@@ -6555,16 +6653,16 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L34">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M34">
         <v>100</v>
       </c>
       <c r="N34">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -6576,16 +6674,16 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S34">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T34">
         <v>100</v>
       </c>
       <c r="U34">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6602,10 +6700,10 @@
         <v>100</v>
       </c>
       <c r="D35">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E35">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F35">
         <v>100</v>
@@ -6623,10 +6721,10 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -6644,10 +6742,10 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T35">
         <v>100</v>
@@ -6670,10 +6768,10 @@
         <v>100</v>
       </c>
       <c r="D36">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E36">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F36">
         <v>100</v>
@@ -6691,10 +6789,10 @@
         <v>100</v>
       </c>
       <c r="K36">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L36">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -6712,10 +6810,10 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T36">
         <v>100</v>
@@ -6738,10 +6836,10 @@
         <v>100</v>
       </c>
       <c r="D37">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F37">
         <v>100</v>
@@ -6759,10 +6857,10 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M37">
         <v>100</v>
@@ -6780,10 +6878,10 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T37">
         <v>100</v>
@@ -6806,10 +6904,10 @@
         <v>100</v>
       </c>
       <c r="D38">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E38">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="F38">
         <v>100</v>
@@ -6827,10 +6925,10 @@
         <v>100</v>
       </c>
       <c r="K38">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L38">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="M38">
         <v>100</v>
@@ -6848,10 +6946,10 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S38">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="T38">
         <v>100</v>
@@ -6874,16 +6972,16 @@
         <v>100</v>
       </c>
       <c r="D39">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E39">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="F39">
         <v>100</v>
       </c>
       <c r="G39">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H39">
         <v>100</v>
@@ -6895,16 +6993,16 @@
         <v>100</v>
       </c>
       <c r="K39">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="L39">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="M39">
         <v>100</v>
       </c>
       <c r="N39">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="O39">
         <v>100</v>
@@ -6916,16 +7014,16 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="T39">
         <v>100</v>
       </c>
       <c r="U39">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V39">
         <v>100</v>
@@ -6936,64 +7034,64 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C40">
         <v>100</v>
       </c>
       <c r="D40">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E40">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="F40">
         <v>100</v>
       </c>
       <c r="G40">
-        <v>37.5</v>
+        <v>93.8</v>
       </c>
       <c r="H40">
         <v>100</v>
       </c>
       <c r="I40">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J40">
         <v>100</v>
       </c>
       <c r="K40">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L40">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="M40">
         <v>100</v>
       </c>
       <c r="N40">
-        <v>37.5</v>
+        <v>93.8</v>
       </c>
       <c r="O40">
         <v>100</v>
       </c>
       <c r="P40">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q40">
         <v>100</v>
       </c>
       <c r="R40">
-        <v>95</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S40">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="T40">
         <v>100</v>
       </c>
       <c r="U40">
-        <v>37.5</v>
+        <v>93.8</v>
       </c>
       <c r="V40">
         <v>100</v>
@@ -7004,64 +7102,64 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C41">
         <v>100</v>
       </c>
       <c r="D41">
-        <v>90</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E41">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="F41">
         <v>100</v>
       </c>
       <c r="G41">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="H41">
         <v>100</v>
       </c>
       <c r="I41">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J41">
         <v>100</v>
       </c>
       <c r="K41">
-        <v>90</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L41">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="M41">
         <v>100</v>
       </c>
       <c r="N41">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="O41">
         <v>100</v>
       </c>
       <c r="P41">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q41">
         <v>100</v>
       </c>
       <c r="R41">
-        <v>90</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S41">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="T41">
         <v>100</v>
       </c>
       <c r="U41">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="V41">
         <v>100</v>
@@ -7078,10 +7176,10 @@
         <v>100</v>
       </c>
       <c r="D42">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="E42">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="F42">
         <v>100</v>
@@ -7099,10 +7197,10 @@
         <v>100</v>
       </c>
       <c r="K42">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="L42">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="M42">
         <v>100</v>
@@ -7120,10 +7218,10 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="S42">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T42">
         <v>100</v>
@@ -7132,6 +7230,74 @@
         <v>100</v>
       </c>
       <c r="V42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43">
+        <v>100</v>
+      </c>
+      <c r="C43">
+        <v>100</v>
+      </c>
+      <c r="D43">
+        <v>87</v>
+      </c>
+      <c r="E43">
+        <v>93.8</v>
+      </c>
+      <c r="F43">
+        <v>100</v>
+      </c>
+      <c r="G43">
+        <v>100</v>
+      </c>
+      <c r="H43">
+        <v>100</v>
+      </c>
+      <c r="I43">
+        <v>100</v>
+      </c>
+      <c r="J43">
+        <v>100</v>
+      </c>
+      <c r="K43">
+        <v>87</v>
+      </c>
+      <c r="L43">
+        <v>93.8</v>
+      </c>
+      <c r="M43">
+        <v>100</v>
+      </c>
+      <c r="N43">
+        <v>100</v>
+      </c>
+      <c r="O43">
+        <v>100</v>
+      </c>
+      <c r="P43">
+        <v>100</v>
+      </c>
+      <c r="Q43">
+        <v>100</v>
+      </c>
+      <c r="R43">
+        <v>87</v>
+      </c>
+      <c r="S43">
+        <v>93.8</v>
+      </c>
+      <c r="T43">
+        <v>100</v>
+      </c>
+      <c r="U43">
+        <v>100</v>
+      </c>
+      <c r="V43">
         <v>100</v>
       </c>
     </row>
@@ -7160,31 +7326,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -7192,22 +7358,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>21</v>
       </c>
       <c r="F2" s="2">
-        <v>46.2</v>
+        <v>47.5</v>
       </c>
       <c r="G2" s="2">
-        <v>53.8</v>
+        <v>52.5</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -7224,22 +7390,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3">
         <v>9</v>
       </c>
       <c r="F3" s="2">
-        <v>76.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="G3" s="2">
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="H3">
         <v>6.4</v>
@@ -7256,22 +7422,22 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>82.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="G4" s="2">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="H4">
         <v>7.2</v>
@@ -7285,13 +7451,13 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>36</v>
@@ -7300,45 +7466,45 @@
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6">
         <v>36</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7349,28 +7515,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="G7" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7384,22 +7550,22 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8">
         <v>39</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H8">
         <v>8.6</v>
@@ -7413,10 +7579,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -7438,7 +7604,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7447,22 +7613,42 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>23330051920261</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -7481,22 +7667,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -7507,19 +7693,19 @@
         <v>23330051920082</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7530,19 +7716,19 @@
         <v>23330051920082</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7553,19 +7739,19 @@
         <v>23330051920083</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7576,19 +7762,19 @@
         <v>23330051920083</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7599,19 +7785,19 @@
         <v>23330051920091</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7622,13 +7808,13 @@
         <v>23330051920091</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -7645,19 +7831,19 @@
         <v>23330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7668,19 +7854,19 @@
         <v>23330051920097</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7691,19 +7877,19 @@
         <v>23330051920105</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7714,19 +7900,19 @@
         <v>23330051920105</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7737,19 +7923,19 @@
         <v>23330051920112</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7760,19 +7946,19 @@
         <v>23330051920112</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7783,19 +7969,19 @@
         <v>23330051920077</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7806,19 +7992,19 @@
         <v>23330051920081</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7829,19 +8015,19 @@
         <v>23330051920086</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7852,19 +8038,19 @@
         <v>23330051920084</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -7875,19 +8061,19 @@
         <v>23330051920090</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -7898,19 +8084,19 @@
         <v>23330051920099</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -7921,19 +8107,19 @@
         <v>23330051920102</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -7944,19 +8130,19 @@
         <v>23330051920103</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -7967,19 +8153,19 @@
         <v>23330051920104</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -7990,19 +8176,19 @@
         <v>23330051920107</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -8013,19 +8199,19 @@
         <v>23330051920110</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G24">
         <v>5</v>

--- a/grupos/1DM - Estadisticos 20231.xlsx
+++ b/grupos/1DM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="115">
   <si>
     <t>Materia</t>
   </si>
@@ -104,7 +104,7 @@
     <t>GONZALEZ ANTONIO YAMILET</t>
   </si>
   <si>
-    <t>GONZALEZ TZNAHUA VIRIDIANA</t>
+    <t>GONZALEZ TZANAHUA VIRIDIANA</t>
   </si>
   <si>
     <t>HERNANDEZ CHAVEZ JOSE ERNESTO</t>
@@ -260,145 +260,109 @@
     <t>ANIELA SAMANTA</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>AZPIRI</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>COCOTLE</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
+    <t>RICO</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>VARILLAS</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
   </si>
   <si>
     <t>CARPINTEYRO</t>
   </si>
   <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>TZNAHUA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>ROMINA GISELLE</t>
+  </si>
+  <si>
+    <t>MELANY</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
   </si>
   <si>
     <t>VALERIA</t>
   </si>
   <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
     <t>MARIA GUADALUPE</t>
   </si>
   <si>
+    <t>JANETH</t>
+  </si>
+  <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
     <t>VIRIDIANA</t>
   </si>
   <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>MELANY</t>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>ANGEL EDUC</t>
-  </si>
-  <si>
-    <t>REY</t>
-  </si>
-  <si>
-    <t>ARELI DANAE</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>HEIDI</t>
   </si>
 </sst>
 </file>
@@ -925,25 +889,25 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -967,16 +931,16 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA4">
         <v>5</v>
@@ -985,7 +949,7 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1014,25 +978,25 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1056,25 +1020,25 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z5">
         <v>10</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB5">
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1103,25 +1067,25 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1148,16 +1112,16 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>9</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB6">
         <v>10</v>
@@ -1192,25 +1156,25 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1234,7 +1198,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1252,7 +1216,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1281,25 +1245,25 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1323,10 +1287,10 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1335,7 +1299,7 @@
         <v>8</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>10</v>
@@ -1370,25 +1334,25 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1412,16 +1376,16 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA9">
         <v>5</v>
@@ -1459,25 +1423,25 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1501,16 +1465,16 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>5</v>
@@ -1548,25 +1512,25 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1590,16 +1554,16 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>5</v>
@@ -1608,7 +1572,7 @@
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1637,25 +1601,25 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1679,10 +1643,10 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1691,13 +1655,13 @@
         <v>9</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>10</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1726,25 +1690,25 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1768,16 +1732,16 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA13">
         <v>5</v>
@@ -1815,25 +1779,25 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1857,7 +1821,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1869,13 +1833,13 @@
         <v>9</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1904,25 +1868,25 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1946,7 +1910,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1955,7 +1919,7 @@
         <v>9</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -1964,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1993,25 +1957,25 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2035,13 +1999,13 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z16">
         <v>10</v>
@@ -2053,7 +2017,7 @@
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2082,25 +2046,25 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2124,13 +2088,13 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z17">
         <v>9</v>
@@ -2171,25 +2135,25 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2213,25 +2177,25 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB18">
         <v>10</v>
       </c>
       <c r="AC18">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2260,25 +2224,25 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2302,13 +2266,13 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>8</v>
@@ -2320,7 +2284,7 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2349,25 +2313,25 @@
         <v>4</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2391,7 +2355,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2400,7 +2364,7 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>5</v>
@@ -2438,25 +2402,25 @@
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2480,13 +2444,13 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z21">
         <v>8</v>
@@ -2498,7 +2462,7 @@
         <v>10</v>
       </c>
       <c r="AC21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2527,25 +2491,25 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2569,16 +2533,16 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA22">
         <v>5</v>
@@ -2587,7 +2551,7 @@
         <v>8</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2616,25 +2580,25 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N23">
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2667,7 +2631,7 @@
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>5</v>
@@ -2705,25 +2669,25 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N24">
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2750,7 +2714,7 @@
         <v>7</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2765,7 +2729,7 @@
         <v>10</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2794,25 +2758,25 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2836,7 +2800,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2848,13 +2812,13 @@
         <v>9</v>
       </c>
       <c r="AA25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB25">
         <v>10</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2883,25 +2847,25 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2925,19 +2889,19 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <v>10</v>
@@ -2972,25 +2936,25 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3014,25 +2978,25 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>9</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB27">
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3061,25 +3025,25 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3103,25 +3067,25 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z28">
         <v>9</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB28">
         <v>9</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3150,25 +3114,25 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3192,19 +3156,19 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>10</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB29">
         <v>10</v>
@@ -3239,25 +3203,25 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3281,19 +3245,19 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB30">
         <v>10</v>
@@ -3328,25 +3292,25 @@
         <v>7</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3370,13 +3334,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z31">
         <v>8</v>
@@ -3417,25 +3381,25 @@
         <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3459,7 +3423,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3506,25 +3470,25 @@
         <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3548,19 +3512,19 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB33">
         <v>-1</v>
@@ -3595,25 +3559,25 @@
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3637,25 +3601,25 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z34">
         <v>10</v>
       </c>
       <c r="AA34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB34">
         <v>10</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3684,25 +3648,25 @@
         <v>9</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3738,13 +3702,13 @@
         <v>9</v>
       </c>
       <c r="AA35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB35">
         <v>10</v>
       </c>
       <c r="AC35">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3773,25 +3737,25 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3815,25 +3779,25 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB36">
         <v>10</v>
       </c>
       <c r="AC36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3862,25 +3826,25 @@
         <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3904,10 +3868,10 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>9</v>
@@ -3916,7 +3880,7 @@
         <v>10</v>
       </c>
       <c r="AA37">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB37">
         <v>10</v>
@@ -3951,25 +3915,25 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N38">
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3993,25 +3957,25 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z38">
         <v>9</v>
       </c>
       <c r="AA38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB38">
         <v>10</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -4040,25 +4004,25 @@
         <v>9</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -4082,7 +4046,7 @@
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>6</v>
@@ -4100,7 +4064,7 @@
         <v>10</v>
       </c>
       <c r="AC39">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -4129,25 +4093,25 @@
         <v>8</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -4171,16 +4135,16 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA40">
         <v>5</v>
@@ -4218,25 +4182,25 @@
         <v>6</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N41">
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4269,7 +4233,7 @@
         <v>5</v>
       </c>
       <c r="Z41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA41">
         <v>5</v>
@@ -4278,7 +4242,7 @@
         <v>5</v>
       </c>
       <c r="AC41">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -4307,25 +4271,25 @@
         <v>9</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N42">
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -4349,7 +4313,7 @@
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X42">
         <v>7</v>
@@ -4396,25 +4360,25 @@
         <v>9</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N43">
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P43">
         <v>-1</v>
@@ -4438,7 +4402,7 @@
         <v>-1</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X43">
         <v>7</v>
@@ -4450,13 +4414,13 @@
         <v>8</v>
       </c>
       <c r="AA43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB43">
         <v>10</v>
       </c>
       <c r="AC43">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4610,16 +4574,16 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="K4">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L4">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -4631,16 +4595,16 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="R4">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S4">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -4681,10 +4645,10 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L5">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -4702,10 +4666,10 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S5">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -4743,19 +4707,19 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>87</v>
+        <v>90.5</v>
       </c>
       <c r="L6">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N6">
         <v>93.8</v>
@@ -4764,19 +4728,19 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>87</v>
+        <v>90.5</v>
       </c>
       <c r="S6">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U6">
         <v>93.8</v>
@@ -4811,40 +4775,40 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L7">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="M7">
+        <v>82.5</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="P7">
         <v>85</v>
       </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
-      <c r="P7">
-        <v>80</v>
-      </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S7">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="T7">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -4879,16 +4843,16 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>82.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L8">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -4900,16 +4864,16 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>82.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S8">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -4947,19 +4911,19 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L9">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N9">
         <v>100</v>
@@ -4968,19 +4932,19 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S9">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -5015,16 +4979,16 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J10">
         <v>100</v>
       </c>
       <c r="K10">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L10">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -5036,16 +5000,16 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S10">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -5089,10 +5053,10 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L11">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -5110,10 +5074,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S11">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -5157,10 +5121,10 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L12">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -5178,10 +5142,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S12">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -5225,10 +5189,10 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>82.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L13">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -5246,10 +5210,10 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>82.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S13">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -5293,10 +5257,10 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L14">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -5314,10 +5278,10 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S14">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T14">
         <v>100</v>
@@ -5361,10 +5325,10 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L15">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -5382,10 +5346,10 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S15">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T15">
         <v>100</v>
@@ -5426,13 +5390,13 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="K16">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L16">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -5447,13 +5411,13 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R16">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S16">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -5497,10 +5461,10 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L17">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -5518,10 +5482,10 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S17">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -5559,16 +5523,16 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>87</v>
+        <v>90.5</v>
       </c>
       <c r="L18">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -5580,16 +5544,16 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>87</v>
+        <v>90.5</v>
       </c>
       <c r="S18">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -5633,10 +5597,10 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="L19">
-        <v>75</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -5654,10 +5618,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="S19">
-        <v>75</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="T19">
         <v>100</v>
@@ -5695,19 +5659,19 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>87</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L20">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="N20">
         <v>93.8</v>
@@ -5716,19 +5680,19 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>87</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S20">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="U20">
         <v>93.8</v>
@@ -5769,10 +5733,10 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L21">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -5790,10 +5754,10 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S21">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -5831,19 +5795,19 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>82.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L22">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="N22">
         <v>93.8</v>
@@ -5852,19 +5816,19 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>82.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="S22">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="U22">
         <v>93.8</v>
@@ -5899,19 +5863,19 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <v>82.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="L23">
-        <v>75</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N23">
         <v>75</v>
@@ -5920,19 +5884,19 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>82.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="S23">
-        <v>75</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U23">
         <v>75</v>
@@ -5973,13 +5937,13 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>78.3</v>
+        <v>81</v>
       </c>
       <c r="L24">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N24">
         <v>100</v>
@@ -5994,13 +5958,13 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>78.3</v>
+        <v>81</v>
       </c>
       <c r="S24">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -6041,10 +6005,10 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L25">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -6062,10 +6026,10 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S25">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -6106,16 +6070,16 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="K26">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L26">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -6127,16 +6091,16 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="R26">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S26">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -6171,19 +6135,19 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J27">
         <v>100</v>
       </c>
       <c r="K27">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L27">
-        <v>93.8</v>
+        <v>90.3</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N27">
         <v>100</v>
@@ -6192,19 +6156,19 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S27">
-        <v>93.8</v>
+        <v>90.3</v>
       </c>
       <c r="T27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -6245,10 +6209,10 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="L28">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -6266,10 +6230,10 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>78.3</v>
+        <v>85.7</v>
       </c>
       <c r="S28">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T28">
         <v>100</v>
@@ -6313,10 +6277,10 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L29">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -6334,10 +6298,10 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S29">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -6375,16 +6339,16 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L30">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -6396,16 +6360,16 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S30">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -6449,10 +6413,10 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L31">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -6470,10 +6434,10 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S31">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -6517,13 +6481,13 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L32">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="M32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N32">
         <v>93.8</v>
@@ -6538,13 +6502,13 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S32">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="T32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U32">
         <v>93.8</v>
@@ -6579,46 +6543,46 @@
         <v>90</v>
       </c>
       <c r="I33">
+        <v>95</v>
+      </c>
+      <c r="J33">
+        <v>100</v>
+      </c>
+      <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="L33">
+        <v>100</v>
+      </c>
+      <c r="M33">
         <v>90</v>
-      </c>
-      <c r="J33">
-        <v>100</v>
-      </c>
-      <c r="K33">
-        <v>100</v>
-      </c>
-      <c r="L33">
-        <v>100</v>
-      </c>
-      <c r="M33">
-        <v>100</v>
       </c>
       <c r="N33">
         <v>0</v>
       </c>
       <c r="O33">
+        <v>95</v>
+      </c>
+      <c r="P33">
+        <v>95</v>
+      </c>
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
+        <v>100</v>
+      </c>
+      <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
         <v>90</v>
-      </c>
-      <c r="P33">
-        <v>90</v>
-      </c>
-      <c r="Q33">
-        <v>100</v>
-      </c>
-      <c r="R33">
-        <v>100</v>
-      </c>
-      <c r="S33">
-        <v>100</v>
-      </c>
-      <c r="T33">
-        <v>100</v>
       </c>
       <c r="U33">
         <v>0</v>
       </c>
       <c r="V33">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6653,10 +6617,10 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L34">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M34">
         <v>100</v>
@@ -6674,10 +6638,10 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S34">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T34">
         <v>100</v>
@@ -6721,10 +6685,10 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>87</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L35">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -6742,10 +6706,10 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>87</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S35">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T35">
         <v>100</v>
@@ -6789,10 +6753,10 @@
         <v>100</v>
       </c>
       <c r="K36">
-        <v>87</v>
+        <v>90.5</v>
       </c>
       <c r="L36">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -6810,10 +6774,10 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>87</v>
+        <v>90.5</v>
       </c>
       <c r="S36">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T36">
         <v>100</v>
@@ -6857,10 +6821,10 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>87</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L37">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M37">
         <v>100</v>
@@ -6878,10 +6842,10 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>87</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S37">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T37">
         <v>100</v>
@@ -6925,10 +6889,10 @@
         <v>100</v>
       </c>
       <c r="K38">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L38">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M38">
         <v>100</v>
@@ -6946,10 +6910,10 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S38">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T38">
         <v>100</v>
@@ -6993,10 +6957,10 @@
         <v>100</v>
       </c>
       <c r="K39">
-        <v>87</v>
+        <v>90.5</v>
       </c>
       <c r="L39">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="M39">
         <v>100</v>
@@ -7014,10 +6978,10 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>87</v>
+        <v>90.5</v>
       </c>
       <c r="S39">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="T39">
         <v>100</v>
@@ -7055,19 +7019,19 @@
         <v>100</v>
       </c>
       <c r="I40">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J40">
         <v>100</v>
       </c>
       <c r="K40">
-        <v>82.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L40">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="M40">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N40">
         <v>93.8</v>
@@ -7076,19 +7040,19 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q40">
         <v>100</v>
       </c>
       <c r="R40">
-        <v>82.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S40">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="T40">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U40">
         <v>93.8</v>
@@ -7129,10 +7093,10 @@
         <v>100</v>
       </c>
       <c r="K41">
-        <v>82.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L41">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="M41">
         <v>100</v>
@@ -7150,10 +7114,10 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>82.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S41">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="T41">
         <v>100</v>
@@ -7197,10 +7161,10 @@
         <v>100</v>
       </c>
       <c r="K42">
-        <v>78.3</v>
+        <v>90.5</v>
       </c>
       <c r="L42">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="M42">
         <v>100</v>
@@ -7218,10 +7182,10 @@
         <v>100</v>
       </c>
       <c r="R42">
-        <v>78.3</v>
+        <v>90.5</v>
       </c>
       <c r="S42">
-        <v>93.8</v>
+        <v>96.8</v>
       </c>
       <c r="T42">
         <v>100</v>
@@ -7265,10 +7229,10 @@
         <v>100</v>
       </c>
       <c r="K43">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="L43">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="M43">
         <v>100</v>
@@ -7286,10 +7250,10 @@
         <v>100</v>
       </c>
       <c r="R43">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="S43">
-        <v>93.8</v>
+        <v>93.5</v>
       </c>
       <c r="T43">
         <v>100</v>
@@ -7364,19 +7328,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2">
-        <v>47.5</v>
+        <v>57.5</v>
       </c>
       <c r="G2" s="2">
-        <v>52.5</v>
+        <v>42.5</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7396,19 +7360,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>77.5</v>
+        <v>80</v>
       </c>
       <c r="G3" s="2">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7428,19 +7392,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>82.5</v>
+        <v>87.5</v>
       </c>
       <c r="G4" s="2">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7504,7 +7468,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7524,19 +7488,19 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="G7" s="2">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7556,19 +7520,19 @@
         <v>40</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7658,7 +7622,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7690,22 +7654,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920082</v>
+        <v>23330051920095</v>
       </c>
       <c r="B2" t="s">
         <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7713,16 +7677,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920082</v>
+        <v>23330051920095</v>
       </c>
       <c r="B3" t="s">
         <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -7736,16 +7700,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920083</v>
+        <v>23330051920105</v>
       </c>
       <c r="B4" t="s">
         <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -7759,16 +7723,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920083</v>
+        <v>23330051920105</v>
       </c>
       <c r="B5" t="s">
         <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -7782,16 +7746,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920091</v>
+        <v>23330051920077</v>
       </c>
       <c r="B6" t="s">
         <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -7805,22 +7769,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920091</v>
+        <v>23330051920079</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7828,22 +7792,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920097</v>
+        <v>23330051920082</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7851,22 +7815,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920097</v>
+        <v>23330051920081</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7874,22 +7838,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920105</v>
+        <v>23330051920083</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7897,16 +7861,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920105</v>
+        <v>23330051920086</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
         <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -7920,22 +7884,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920112</v>
+        <v>23330051920084</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7943,16 +7907,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920112</v>
+        <v>23330051920091</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -7966,16 +7930,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920077</v>
+        <v>23330051920104</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
         <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -7989,16 +7953,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920081</v>
+        <v>23330051920112</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
         <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -8007,213 +7971,6 @@
         <v>66</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920086</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920084</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920090</v>
-      </c>
-      <c r="B18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920099</v>
-      </c>
-      <c r="B19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>121</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920102</v>
-      </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>66</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920103</v>
-      </c>
-      <c r="B21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920104</v>
-      </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920107</v>
-      </c>
-      <c r="B23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920110</v>
-      </c>
-      <c r="B24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20231.xlsx
+++ b/grupos/1DM - Estadisticos 20231.xlsx
@@ -904,7 +904,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>7</v>
@@ -993,7 +993,7 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -1035,7 +1035,7 @@
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>8</v>
@@ -1082,7 +1082,7 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>7</v>
@@ -1171,7 +1171,7 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1260,7 +1260,7 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1302,7 +1302,7 @@
         <v>7</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>7</v>
@@ -1349,7 +1349,7 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -1438,7 +1438,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1480,7 +1480,7 @@
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>7</v>
@@ -1527,7 +1527,7 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1569,7 +1569,7 @@
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>7</v>
@@ -1616,7 +1616,7 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1705,7 +1705,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1794,7 +1794,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -1883,7 +1883,7 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>6</v>
@@ -1972,7 +1972,7 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -2061,7 +2061,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>8</v>
@@ -2103,7 +2103,7 @@
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>9</v>
@@ -2150,7 +2150,7 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -2239,7 +2239,7 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -2281,7 +2281,7 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>6</v>
@@ -2328,7 +2328,7 @@
         <v>4</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>4</v>
@@ -2370,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -2417,7 +2417,7 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>7</v>
@@ -2459,7 +2459,7 @@
         <v>8</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -2506,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>4</v>
@@ -2548,7 +2548,7 @@
         <v>5</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>6</v>
@@ -2595,7 +2595,7 @@
         <v>4</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>4</v>
@@ -2684,7 +2684,7 @@
         <v>4</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2773,7 +2773,7 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>8</v>
@@ -2862,7 +2862,7 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>9</v>
@@ -2951,7 +2951,7 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>6</v>
@@ -2993,7 +2993,7 @@
         <v>8</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -3040,7 +3040,7 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -3082,7 +3082,7 @@
         <v>7</v>
       </c>
       <c r="AB28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC28">
         <v>8</v>
@@ -3129,7 +3129,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>9</v>
@@ -3218,7 +3218,7 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>7</v>
@@ -3260,7 +3260,7 @@
         <v>6</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -3349,7 +3349,7 @@
         <v>5</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>7</v>
@@ -3396,7 +3396,7 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>7</v>
@@ -3438,7 +3438,7 @@
         <v>5</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>8</v>
@@ -3574,7 +3574,7 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>8</v>
@@ -3663,7 +3663,7 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>6</v>
@@ -3752,7 +3752,7 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>8</v>
@@ -3841,7 +3841,7 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>9</v>
@@ -3930,7 +3930,7 @@
         <v>7</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>6</v>
@@ -4019,7 +4019,7 @@
         <v>7</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>7</v>
@@ -4108,7 +4108,7 @@
         <v>5</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>7</v>
@@ -4150,7 +4150,7 @@
         <v>5</v>
       </c>
       <c r="AB40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC40">
         <v>8</v>
@@ -4197,7 +4197,7 @@
         <v>4</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>4</v>
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>9</v>
@@ -4328,7 +4328,7 @@
         <v>10</v>
       </c>
       <c r="AB42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC42">
         <v>9</v>
@@ -4375,7 +4375,7 @@
         <v>8</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O43">
         <v>7</v>
@@ -4722,7 +4722,7 @@
         <v>90</v>
       </c>
       <c r="N6">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -4743,7 +4743,7 @@
         <v>90</v>
       </c>
       <c r="U6">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -4858,7 +4858,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4879,7 +4879,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -5606,7 +5606,7 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -5627,7 +5627,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -5810,7 +5810,7 @@
         <v>92.5</v>
       </c>
       <c r="N22">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -5831,7 +5831,7 @@
         <v>92.5</v>
       </c>
       <c r="U22">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -5878,7 +5878,7 @@
         <v>90</v>
       </c>
       <c r="N23">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -5899,7 +5899,7 @@
         <v>90</v>
       </c>
       <c r="U23">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -6218,7 +6218,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -6239,7 +6239,7 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -6286,7 +6286,7 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -6307,7 +6307,7 @@
         <v>100</v>
       </c>
       <c r="U29">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6422,7 +6422,7 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -6443,7 +6443,7 @@
         <v>100</v>
       </c>
       <c r="U31">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -6626,7 +6626,7 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -6647,7 +6647,7 @@
         <v>100</v>
       </c>
       <c r="U34">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6966,7 +6966,7 @@
         <v>100</v>
       </c>
       <c r="N39">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O39">
         <v>100</v>
@@ -6987,7 +6987,7 @@
         <v>100</v>
       </c>
       <c r="U39">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V39">
         <v>100</v>
@@ -7102,7 +7102,7 @@
         <v>100</v>
       </c>
       <c r="N41">
-        <v>37.5</v>
+        <v>68.8</v>
       </c>
       <c r="O41">
         <v>100</v>
@@ -7123,7 +7123,7 @@
         <v>100</v>
       </c>
       <c r="U41">
-        <v>37.5</v>
+        <v>68.8</v>
       </c>
       <c r="V41">
         <v>100</v>
@@ -7436,7 +7436,7 @@
         <v>7.5</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>1</v>

--- a/grupos/1DM - Estadisticos 20231.xlsx
+++ b/grupos/1DM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="112">
   <si>
     <t>Materia</t>
   </si>
@@ -249,15 +249,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>ANIELA SAMANTA</t>
   </si>
   <si>
     <t>HUERTA</t>
@@ -3307,7 +3298,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -3349,7 +3340,7 @@
         <v>5</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC31">
         <v>7</v>
@@ -3464,7 +3455,7 @@
         <v>6</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H33">
         <v>5</v>
@@ -3485,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>5</v>
@@ -3527,7 +3518,7 @@
         <v>5</v>
       </c>
       <c r="AB33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC33">
         <v>5</v>
@@ -6537,7 +6528,7 @@
         <v>100</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="H33">
         <v>90</v>
@@ -6558,7 +6549,7 @@
         <v>90</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="O33">
         <v>95</v>
@@ -6579,7 +6570,7 @@
         <v>90</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="V33">
         <v>95</v>
@@ -7427,22 +7418,22 @@
         <v>36</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
         <v>90</v>
       </c>
       <c r="G5" s="2">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7568,7 +7559,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7593,26 +7584,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920261</v>
-      </c>
-      <c r="B2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -7657,13 +7628,13 @@
         <v>23330051920095</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7680,13 +7651,13 @@
         <v>23330051920095</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -7703,13 +7674,13 @@
         <v>23330051920105</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -7726,13 +7697,13 @@
         <v>23330051920105</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -7749,13 +7720,13 @@
         <v>23330051920077</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -7772,13 +7743,13 @@
         <v>23330051920079</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -7795,13 +7766,13 @@
         <v>23330051920082</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -7818,13 +7789,13 @@
         <v>23330051920081</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -7841,13 +7812,13 @@
         <v>23330051920083</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -7864,13 +7835,13 @@
         <v>23330051920086</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -7887,13 +7858,13 @@
         <v>23330051920084</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -7910,13 +7881,13 @@
         <v>23330051920091</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -7933,13 +7904,13 @@
         <v>23330051920104</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -7956,13 +7927,13 @@
         <v>23330051920112</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>

--- a/grupos/1DM - Estadisticos 20231.xlsx
+++ b/grupos/1DM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="97">
   <si>
     <t>Materia</t>
   </si>
@@ -227,12 +227,12 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Santiago Hernández Mariana</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Santiago Hernández Mariana</t>
-  </si>
-  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
@@ -251,106 +251,61 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>HUERTA</t>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>AZPIRI</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>RICO</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>AZPIRI</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>BERISTAIN</t>
   </si>
   <si>
     <t>OLMOS</t>
   </si>
   <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
+    <t>GUEVARA</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>ROMINA GISELLE</t>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>MELANY</t>
   </si>
   <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
+    <t>ANIELA SAMANTA</t>
   </si>
   <si>
     <t>MARGARITA</t>
@@ -901,25 +856,25 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -934,10 +889,10 @@
         <v>9</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>9</v>
@@ -990,25 +945,25 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1029,7 +984,7 @@
         <v>9</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1079,46 +1034,46 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>8</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA6">
         <v>5</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1168,46 +1123,46 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>8</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1257,46 +1212,46 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>9</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>7</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1346,25 +1301,25 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1373,16 +1328,16 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -1435,43 +1390,43 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>9</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>7</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>7</v>
@@ -1524,25 +1479,25 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1560,10 +1515,10 @@
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1613,25 +1568,25 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1646,10 +1601,10 @@
         <v>9</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>8</v>
@@ -1702,46 +1657,46 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1791,25 +1746,25 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1830,7 +1785,7 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1880,31 +1835,31 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1916,10 +1871,10 @@
         <v>6</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1969,25 +1924,25 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1996,7 +1951,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z16">
         <v>10</v>
@@ -2005,10 +1960,10 @@
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2058,25 +2013,25 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2085,7 +2040,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>9</v>
@@ -2147,31 +2102,31 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2183,7 +2138,7 @@
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -2236,46 +2191,46 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2325,25 +2280,25 @@
         <v>4</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2361,7 +2316,7 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -2414,31 +2369,31 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2503,43 +2458,43 @@
         <v>4</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC22">
         <v>6</v>
@@ -2592,25 +2547,25 @@
         <v>4</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2622,7 +2577,7 @@
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA23">
         <v>5</v>
@@ -2681,25 +2636,25 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2708,7 +2663,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z24">
         <v>8</v>
@@ -2717,10 +2672,10 @@
         <v>5</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2770,25 +2725,25 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2797,16 +2752,16 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>9</v>
       </c>
       <c r="AA25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>9</v>
@@ -2859,25 +2814,25 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2889,7 +2844,7 @@
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>7</v>
@@ -2948,40 +2903,40 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>8</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>9</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>8</v>
@@ -3037,25 +2992,25 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -3067,13 +3022,13 @@
         <v>9</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC28">
         <v>8</v>
@@ -3126,25 +3081,25 @@
         <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3159,13 +3114,13 @@
         <v>10</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3215,25 +3170,25 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3242,7 +3197,7 @@
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z30">
         <v>8</v>
@@ -3251,10 +3206,10 @@
         <v>6</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3304,25 +3259,25 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3340,7 +3295,7 @@
         <v>5</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>7</v>
@@ -3393,43 +3348,43 @@
         <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>9</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>5</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC32">
         <v>8</v>
@@ -3482,28 +3437,28 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>6</v>
@@ -3518,10 +3473,10 @@
         <v>5</v>
       </c>
       <c r="AB33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3571,25 +3526,25 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3660,25 +3615,25 @@
         <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3749,25 +3704,25 @@
         <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>10</v>
@@ -3776,7 +3731,7 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z36">
         <v>10</v>
@@ -3838,25 +3793,25 @@
         <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3871,7 +3826,7 @@
         <v>10</v>
       </c>
       <c r="AA37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB37">
         <v>10</v>
@@ -3927,25 +3882,25 @@
         <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3954,7 +3909,7 @@
         <v>8</v>
       </c>
       <c r="Y38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z38">
         <v>9</v>
@@ -3966,7 +3921,7 @@
         <v>10</v>
       </c>
       <c r="AC38">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -4016,25 +3971,25 @@
         <v>7</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W39">
         <v>10</v>
@@ -4055,7 +4010,7 @@
         <v>10</v>
       </c>
       <c r="AC39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -4105,28 +4060,28 @@
         <v>7</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>6</v>
@@ -4141,10 +4096,10 @@
         <v>5</v>
       </c>
       <c r="AB40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC40">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -4194,28 +4149,28 @@
         <v>4</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X41">
         <v>5</v>
@@ -4224,7 +4179,7 @@
         <v>5</v>
       </c>
       <c r="Z41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA41">
         <v>5</v>
@@ -4283,31 +4238,31 @@
         <v>9</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y42">
         <v>8</v>
@@ -4319,7 +4274,7 @@
         <v>10</v>
       </c>
       <c r="AB42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC42">
         <v>9</v>
@@ -4372,25 +4327,25 @@
         <v>7</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W43">
         <v>9</v>
@@ -4411,7 +4366,7 @@
         <v>10</v>
       </c>
       <c r="AC43">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4586,19 +4541,19 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="R4">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S4">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T4">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -4657,16 +4612,16 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S5">
-        <v>93.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T5">
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4719,22 +4674,22 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R6">
-        <v>90.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="S6">
-        <v>96.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T6">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="U6">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -4787,22 +4742,22 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S7">
-        <v>90.3</v>
+        <v>91.8</v>
       </c>
       <c r="T7">
-        <v>82.5</v>
+        <v>88.3</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -4855,22 +4810,22 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>92.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S8">
-        <v>96.8</v>
+        <v>91.8</v>
       </c>
       <c r="T8">
         <v>100</v>
       </c>
       <c r="U8">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4923,22 +4878,22 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>95.2</v>
+        <v>95.5</v>
       </c>
       <c r="S9">
-        <v>96.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T9">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="U9">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -4991,22 +4946,22 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R10">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S10">
-        <v>93.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T10">
         <v>100</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -5065,16 +5020,16 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S11">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T11">
         <v>100</v>
       </c>
       <c r="U11">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -5133,16 +5088,16 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S12">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T12">
         <v>100</v>
       </c>
       <c r="U12">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -5195,22 +5150,22 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="S13">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T13">
         <v>100</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -5269,16 +5224,16 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S14">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T14">
         <v>100</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -5337,16 +5292,16 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S15">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T15">
         <v>100</v>
       </c>
       <c r="U15">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -5402,19 +5357,19 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R16">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S16">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T16">
         <v>100</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -5473,10 +5428,10 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S17">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -5535,22 +5490,22 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R18">
-        <v>90.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="S18">
-        <v>96.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T18">
         <v>100</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5603,22 +5558,22 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>85.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S19">
-        <v>83.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="T19">
         <v>100</v>
       </c>
       <c r="U19">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -5671,22 +5626,22 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R20">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="S20">
-        <v>87.09999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="T20">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="U20">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -5745,10 +5700,10 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>95.2</v>
+        <v>95.5</v>
       </c>
       <c r="S21">
-        <v>96.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -5807,22 +5762,22 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>88.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="S22">
-        <v>93.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T22">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="U22">
-        <v>90.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -5875,25 +5830,25 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>65</v>
+        <v>43.3</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="R23">
-        <v>83.3</v>
+        <v>53</v>
       </c>
       <c r="S23">
-        <v>83.90000000000001</v>
+        <v>53.1</v>
       </c>
       <c r="T23">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U23">
-        <v>78.09999999999999</v>
+        <v>54.2</v>
       </c>
       <c r="V23">
-        <v>100</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5946,19 +5901,19 @@
         <v>80</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R24">
-        <v>81</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="S24">
-        <v>90.3</v>
+        <v>89.8</v>
       </c>
       <c r="T24">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -6017,16 +5972,16 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S25">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T25">
         <v>100</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -6079,22 +6034,22 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q26">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="R26">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S26">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T26">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -6147,19 +6102,19 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
-        <v>95.2</v>
+        <v>95.5</v>
       </c>
       <c r="S27">
-        <v>90.3</v>
+        <v>91.8</v>
       </c>
       <c r="T27">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -6221,16 +6176,16 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>85.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="S28">
-        <v>96.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T28">
         <v>100</v>
       </c>
       <c r="U28">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -6289,16 +6244,16 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S29">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T29">
         <v>100</v>
       </c>
       <c r="U29">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6351,22 +6306,22 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S30">
-        <v>93.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T30">
         <v>100</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -6425,16 +6380,16 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S31">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T31">
         <v>100</v>
       </c>
       <c r="U31">
-        <v>93.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -6490,19 +6445,19 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R32">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S32">
-        <v>93.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="T32">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U32">
-        <v>93.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -6555,10 +6510,10 @@
         <v>95</v>
       </c>
       <c r="P33">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -6567,13 +6522,13 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U33">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="V33">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6629,16 +6584,16 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S34">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T34">
         <v>100</v>
       </c>
       <c r="U34">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6697,10 +6652,10 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="S35">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T35">
         <v>100</v>
@@ -6765,10 +6720,10 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>90.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="S36">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T36">
         <v>100</v>
@@ -6833,10 +6788,10 @@
         <v>100</v>
       </c>
       <c r="R37">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="S37">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T37">
         <v>100</v>
@@ -6901,10 +6856,10 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S38">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T38">
         <v>100</v>
@@ -6969,10 +6924,10 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>90.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="S39">
-        <v>93.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T39">
         <v>100</v>
@@ -7031,16 +6986,16 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="Q40">
         <v>100</v>
       </c>
       <c r="R40">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="S40">
-        <v>93.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T40">
         <v>90</v>
@@ -7099,22 +7054,22 @@
         <v>100</v>
       </c>
       <c r="P41">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="Q41">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R41">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="S41">
-        <v>93.5</v>
+        <v>91.8</v>
       </c>
       <c r="T41">
         <v>100</v>
       </c>
       <c r="U41">
-        <v>68.8</v>
+        <v>56.3</v>
       </c>
       <c r="V41">
         <v>100</v>
@@ -7170,19 +7125,19 @@
         <v>100</v>
       </c>
       <c r="Q42">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R42">
-        <v>90.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="S42">
-        <v>96.8</v>
+        <v>98</v>
       </c>
       <c r="T42">
         <v>100</v>
       </c>
       <c r="U42">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="V42">
         <v>100</v>
@@ -7241,10 +7196,10 @@
         <v>100</v>
       </c>
       <c r="R43">
-        <v>95.2</v>
+        <v>97</v>
       </c>
       <c r="S43">
-        <v>93.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T43">
         <v>100</v>
@@ -7319,16 +7274,16 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>57.5</v>
+        <v>75</v>
       </c>
       <c r="G2" s="2">
-        <v>42.5</v>
+        <v>25</v>
       </c>
       <c r="H2">
         <v>6.5</v>
@@ -7351,16 +7306,16 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H3">
         <v>6.7</v>
@@ -7383,16 +7338,16 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>87.5</v>
+        <v>92.5</v>
       </c>
       <c r="G4" s="2">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -7406,7 +7361,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -7415,19 +7370,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="G5" s="2">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7438,7 +7393,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -7447,19 +7402,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G6" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7479,16 +7434,16 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="G7" s="2">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="H7">
         <v>8.800000000000001</v>
@@ -7511,19 +7466,19 @@
         <v>40</v>
       </c>
       <c r="D8">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7593,7 +7548,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7625,16 +7580,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920095</v>
+        <v>23330051920097</v>
       </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7648,16 +7603,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920095</v>
+        <v>23330051920097</v>
       </c>
       <c r="B3" t="s">
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -7671,22 +7626,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920105</v>
+        <v>23330051920079</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7694,16 +7649,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920105</v>
+        <v>23330051920084</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -7717,16 +7672,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920077</v>
+        <v>23330051920104</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -7740,16 +7695,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920079</v>
+        <v>23330051920105</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -7763,16 +7718,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920082</v>
+        <v>23330051920261</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -7786,162 +7741,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920081</v>
+        <v>23330051920112</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920083</v>
-      </c>
-      <c r="B10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920086</v>
-      </c>
-      <c r="B11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>107</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920084</v>
-      </c>
-      <c r="B12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920091</v>
-      </c>
-      <c r="B13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920104</v>
-      </c>
-      <c r="B14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920112</v>
-      </c>
-      <c r="B15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20231.xlsx
+++ b/grupos/1DM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="97">
   <si>
     <t>Materia</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Recursos socioemocionales I</t>
+  </si>
+  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -213,9 +216,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>Recursos socioemocionales I</t>
   </si>
   <si>
     <t>Duran Amezcua María Angélica</t>
@@ -670,13 +670,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC43"/>
+  <dimension ref="A1:AG43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -687,35 +687,39 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -741,77 +745,89 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AG2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -838,69 +854,81 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>9</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z4">
         <v>9</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="AD4">
+        <v>6</v>
+      </c>
+      <c r="AE4">
+        <v>9</v>
+      </c>
+      <c r="AF4">
+        <v>9</v>
+      </c>
+      <c r="AG4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>9</v>
@@ -927,52 +955,52 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z5">
         <v>10</v>
@@ -984,12 +1012,24 @@
         <v>9</v>
       </c>
       <c r="AC5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD5">
+        <v>7</v>
+      </c>
+      <c r="AE5">
+        <v>9</v>
+      </c>
+      <c r="AF5">
+        <v>9</v>
+      </c>
+      <c r="AG5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -1013,72 +1053,84 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>9</v>
       </c>
       <c r="S6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z6">
         <v>8</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD6">
+        <v>5</v>
+      </c>
+      <c r="AE6">
+        <v>8</v>
+      </c>
+      <c r="AF6">
+        <v>7</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1102,72 +1154,84 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>8</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
+        <v>9</v>
+      </c>
+      <c r="W7">
+        <v>7</v>
+      </c>
+      <c r="X7">
         <v>4</v>
       </c>
-      <c r="W7">
-        <v>6</v>
-      </c>
-      <c r="X7">
-        <v>6</v>
-      </c>
       <c r="Y7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>6</v>
       </c>
       <c r="AB7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD7">
+        <v>6</v>
+      </c>
+      <c r="AE7">
+        <v>6</v>
+      </c>
+      <c r="AF7">
+        <v>6</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1194,69 +1258,81 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>5</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD8">
+        <v>7</v>
+      </c>
+      <c r="AE8">
+        <v>7</v>
+      </c>
+      <c r="AF8">
+        <v>6</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -1283,69 +1359,81 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z9">
         <v>9</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD9">
+        <v>6</v>
+      </c>
+      <c r="AE9">
+        <v>9</v>
+      </c>
+      <c r="AF9">
+        <v>8</v>
+      </c>
+      <c r="AG9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -1372,55 +1460,55 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>8</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA10">
         <v>6</v>
@@ -1431,10 +1519,22 @@
       <c r="AC10">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:29">
+      <c r="AD10">
+        <v>6</v>
+      </c>
+      <c r="AE10">
+        <v>7</v>
+      </c>
+      <c r="AF10">
+        <v>7</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -1461,58 +1561,58 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>8</v>
       </c>
       <c r="S11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB11">
         <v>7</v>
@@ -1520,10 +1620,22 @@
       <c r="AC11">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11">
+        <v>5</v>
+      </c>
+      <c r="AE11">
+        <v>7</v>
+      </c>
+      <c r="AF11">
+        <v>8</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>9</v>
@@ -1550,69 +1662,81 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>9</v>
       </c>
       <c r="AC12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD12">
+        <v>7</v>
+      </c>
+      <c r="AE12">
+        <v>9</v>
+      </c>
+      <c r="AF12">
+        <v>8</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>7</v>
@@ -1636,55 +1760,55 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z13">
         <v>9</v>
@@ -1693,15 +1817,27 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD13">
+        <v>6</v>
+      </c>
+      <c r="AE13">
+        <v>9</v>
+      </c>
+      <c r="AF13">
+        <v>7</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>9</v>
@@ -1728,16 +1864,16 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>10</v>
@@ -1749,48 +1885,60 @@
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:29">
+      <c r="AD14">
+        <v>9</v>
+      </c>
+      <c r="AE14">
+        <v>10</v>
+      </c>
+      <c r="AF14">
+        <v>9</v>
+      </c>
+      <c r="AG14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>9</v>
@@ -1817,7 +1965,7 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>8</v>
@@ -1826,49 +1974,49 @@
         <v>8</v>
       </c>
       <c r="M15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>9</v>
       </c>
       <c r="S15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>9</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z15">
         <v>9</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>9</v>
@@ -1876,10 +2024,22 @@
       <c r="AC15">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:29">
+      <c r="AD15">
+        <v>6</v>
+      </c>
+      <c r="AE15">
+        <v>9</v>
+      </c>
+      <c r="AF15">
+        <v>9</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>9</v>
@@ -1906,69 +2066,81 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z16">
         <v>10</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD16">
+        <v>6</v>
+      </c>
+      <c r="AE16">
+        <v>9</v>
+      </c>
+      <c r="AF16">
+        <v>7</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>9</v>
@@ -1995,10 +2167,10 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -2007,57 +2179,69 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>8</v>
       </c>
       <c r="P17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>10</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:29">
+      <c r="AD17">
+        <v>9</v>
+      </c>
+      <c r="AE17">
+        <v>9</v>
+      </c>
+      <c r="AF17">
+        <v>9</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>8</v>
@@ -2081,72 +2265,84 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>8</v>
       </c>
       <c r="M18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>6</v>
       </c>
       <c r="Q18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>8</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>8</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD18">
+        <v>6</v>
+      </c>
+      <c r="AE18">
+        <v>9</v>
+      </c>
+      <c r="AF18">
+        <v>8</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>7</v>
@@ -2170,72 +2366,84 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>9</v>
       </c>
       <c r="K19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>7</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:29">
+      <c r="AD19">
+        <v>6</v>
+      </c>
+      <c r="AE19">
+        <v>9</v>
+      </c>
+      <c r="AF19">
+        <v>7</v>
+      </c>
+      <c r="AG19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>5</v>
@@ -2259,72 +2467,84 @@
         <v>4</v>
       </c>
       <c r="I20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K20">
+        <v>5</v>
+      </c>
+      <c r="L20">
         <v>4</v>
       </c>
-      <c r="L20">
-        <v>5</v>
-      </c>
       <c r="M20">
+        <v>5</v>
+      </c>
+      <c r="N20">
         <v>4</v>
       </c>
-      <c r="N20">
-        <v>5</v>
-      </c>
       <c r="O20">
+        <v>5</v>
+      </c>
+      <c r="P20">
         <v>4</v>
       </c>
-      <c r="P20">
-        <v>7</v>
-      </c>
       <c r="Q20">
         <v>5</v>
       </c>
       <c r="R20">
+        <v>7</v>
+      </c>
+      <c r="S20">
+        <v>5</v>
+      </c>
+      <c r="T20">
         <v>2</v>
       </c>
-      <c r="S20">
-        <v>7</v>
-      </c>
-      <c r="T20">
-        <v>6</v>
-      </c>
       <c r="U20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD20">
+        <v>5</v>
+      </c>
+      <c r="AE20">
+        <v>6</v>
+      </c>
+      <c r="AF20">
+        <v>5</v>
+      </c>
+      <c r="AG20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>9</v>
@@ -2351,69 +2571,81 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>8</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>7</v>
       </c>
       <c r="Q21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>8</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:29">
+      <c r="AD21">
+        <v>8</v>
+      </c>
+      <c r="AE21">
+        <v>8</v>
+      </c>
+      <c r="AF21">
+        <v>8</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>6</v>
@@ -2437,16 +2669,16 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2455,37 +2687,37 @@
         <v>5</v>
       </c>
       <c r="O22">
+        <v>5</v>
+      </c>
+      <c r="P22">
         <v>4</v>
       </c>
-      <c r="P22">
-        <v>6</v>
-      </c>
       <c r="Q22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>8</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -2494,15 +2726,27 @@
         <v>6</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD22">
+        <v>6</v>
+      </c>
+      <c r="AE22">
+        <v>6</v>
+      </c>
+      <c r="AF22">
+        <v>6</v>
+      </c>
+      <c r="AG22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>4</v>
@@ -2532,47 +2776,47 @@
         <v>5</v>
       </c>
       <c r="K23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23">
+        <v>5</v>
+      </c>
+      <c r="N23">
         <v>4</v>
       </c>
-      <c r="N23">
-        <v>5</v>
-      </c>
       <c r="O23">
+        <v>5</v>
+      </c>
+      <c r="P23">
         <v>4</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
+        <v>5</v>
+      </c>
+      <c r="R23">
         <v>3</v>
       </c>
-      <c r="Q23">
-        <v>5</v>
-      </c>
-      <c r="R23">
+      <c r="S23">
+        <v>5</v>
+      </c>
+      <c r="T23">
         <v>0</v>
       </c>
-      <c r="S23">
-        <v>5</v>
-      </c>
-      <c r="T23">
-        <v>5</v>
-      </c>
       <c r="U23">
         <v>5</v>
       </c>
       <c r="V23">
+        <v>5</v>
+      </c>
+      <c r="W23">
+        <v>5</v>
+      </c>
+      <c r="X23">
         <v>1</v>
       </c>
-      <c r="W23">
-        <v>5</v>
-      </c>
-      <c r="X23">
-        <v>5</v>
-      </c>
       <c r="Y23">
         <v>5</v>
       </c>
@@ -2588,10 +2832,22 @@
       <c r="AC23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:29">
+      <c r="AD23">
+        <v>5</v>
+      </c>
+      <c r="AE23">
+        <v>5</v>
+      </c>
+      <c r="AF23">
+        <v>5</v>
+      </c>
+      <c r="AG23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>7</v>
@@ -2615,43 +2871,43 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>5</v>
       </c>
       <c r="L24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M24">
+        <v>8</v>
+      </c>
+      <c r="N24">
         <v>4</v>
       </c>
-      <c r="N24">
-        <v>9</v>
-      </c>
       <c r="O24">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2663,24 +2919,36 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>5</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC24">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD24">
+        <v>5</v>
+      </c>
+      <c r="AE24">
+        <v>9</v>
+      </c>
+      <c r="AF24">
+        <v>7</v>
+      </c>
+      <c r="AG24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>9</v>
@@ -2707,69 +2975,81 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>9</v>
       </c>
       <c r="N25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T25">
         <v>8</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>8</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="1:29">
+      <c r="AD25">
+        <v>8</v>
+      </c>
+      <c r="AE25">
+        <v>9</v>
+      </c>
+      <c r="AF25">
+        <v>9</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>8</v>
@@ -2796,69 +3076,81 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>9</v>
       </c>
       <c r="Q26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>8</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>9</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>7</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC26">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD26">
+        <v>7</v>
+      </c>
+      <c r="AE26">
+        <v>10</v>
+      </c>
+      <c r="AF26">
+        <v>9</v>
+      </c>
+      <c r="AG26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>9</v>
@@ -2882,55 +3174,55 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>8</v>
       </c>
       <c r="L27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>6</v>
       </c>
       <c r="N27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>9</v>
       </c>
       <c r="S27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z27">
         <v>8</v>
@@ -2939,15 +3231,27 @@
         <v>7</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC27">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="1:29">
+      <c r="AD27">
+        <v>7</v>
+      </c>
+      <c r="AE27">
+        <v>8</v>
+      </c>
+      <c r="AF27">
+        <v>8</v>
+      </c>
+      <c r="AG27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>8</v>
@@ -2974,43 +3278,43 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>9</v>
       </c>
       <c r="S28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -3019,13 +3323,13 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB28">
         <v>9</v>
@@ -3033,10 +3337,22 @@
       <c r="AC28">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:29">
+      <c r="AD28">
+        <v>6</v>
+      </c>
+      <c r="AE28">
+        <v>9</v>
+      </c>
+      <c r="AF28">
+        <v>8</v>
+      </c>
+      <c r="AG28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>8</v>
@@ -3063,13 +3379,13 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -3078,54 +3394,66 @@
         <v>10</v>
       </c>
       <c r="O29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>10</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA29">
         <v>7</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC29">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD29">
+        <v>7</v>
+      </c>
+      <c r="AE29">
+        <v>10</v>
+      </c>
+      <c r="AF29">
+        <v>9</v>
+      </c>
+      <c r="AG29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>7</v>
@@ -3152,10 +3480,10 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>7</v>
@@ -3164,57 +3492,69 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>6</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA30">
         <v>6</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC30">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD30">
+        <v>6</v>
+      </c>
+      <c r="AE30">
+        <v>7</v>
+      </c>
+      <c r="AF30">
+        <v>7</v>
+      </c>
+      <c r="AG30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>8</v>
@@ -3241,69 +3581,81 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>10</v>
       </c>
       <c r="S31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC31">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD31">
+        <v>5</v>
+      </c>
+      <c r="AE31">
+        <v>8</v>
+      </c>
+      <c r="AF31">
+        <v>7</v>
+      </c>
+      <c r="AG31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>8</v>
@@ -3330,58 +3682,58 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>5</v>
       </c>
       <c r="O32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>8</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB32">
         <v>7</v>
@@ -3389,10 +3741,22 @@
       <c r="AC32">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:29">
+      <c r="AD32">
+        <v>5</v>
+      </c>
+      <c r="AE32">
+        <v>7</v>
+      </c>
+      <c r="AF32">
+        <v>8</v>
+      </c>
+      <c r="AG32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>6</v>
@@ -3419,16 +3783,16 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>8</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>5</v>
@@ -3437,51 +3801,63 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD33">
+        <v>5</v>
+      </c>
+      <c r="AE33">
+        <v>7</v>
+      </c>
+      <c r="AF33">
+        <v>6</v>
+      </c>
+      <c r="AG33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>9</v>
@@ -3508,10 +3884,10 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3523,34 +3899,34 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
       </c>
       <c r="S34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U34">
         <v>10</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>10</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3565,12 +3941,24 @@
         <v>10</v>
       </c>
       <c r="AC34">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD34">
+        <v>9</v>
+      </c>
+      <c r="AE34">
+        <v>10</v>
+      </c>
+      <c r="AF34">
+        <v>9</v>
+      </c>
+      <c r="AG34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>9</v>
@@ -3594,55 +3982,55 @@
         <v>9</v>
       </c>
       <c r="I35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L35">
         <v>8</v>
       </c>
       <c r="M35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>9</v>
       </c>
       <c r="S35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z35">
         <v>9</v>
@@ -3651,15 +4039,27 @@
         <v>7</v>
       </c>
       <c r="AB35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC35">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD35">
+        <v>7</v>
+      </c>
+      <c r="AE35">
+        <v>10</v>
+      </c>
+      <c r="AF35">
+        <v>8</v>
+      </c>
+      <c r="AG35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>9</v>
@@ -3686,10 +4086,10 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>10</v>
@@ -3701,22 +4101,22 @@
         <v>10</v>
       </c>
       <c r="O36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>10</v>
@@ -3728,10 +4128,10 @@
         <v>10</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z36">
         <v>10</v>
@@ -3740,15 +4140,27 @@
         <v>9</v>
       </c>
       <c r="AB36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC36">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD36">
+        <v>9</v>
+      </c>
+      <c r="AE36">
+        <v>10</v>
+      </c>
+      <c r="AF36">
+        <v>9</v>
+      </c>
+      <c r="AG36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>9</v>
@@ -3778,10 +4190,10 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M37">
         <v>10</v>
@@ -3790,54 +4202,66 @@
         <v>10</v>
       </c>
       <c r="O37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>10</v>
       </c>
       <c r="S37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>10</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>10</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z37">
         <v>10</v>
       </c>
       <c r="AA37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC37">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:29">
+      <c r="AD37">
+        <v>8</v>
+      </c>
+      <c r="AE37">
+        <v>10</v>
+      </c>
+      <c r="AF37">
+        <v>10</v>
+      </c>
+      <c r="AG37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>9</v>
@@ -3864,69 +4288,81 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>9</v>
       </c>
       <c r="L38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>10</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC38">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" spans="1:29">
+      <c r="AD38">
+        <v>6</v>
+      </c>
+      <c r="AE38">
+        <v>10</v>
+      </c>
+      <c r="AF38">
+        <v>9</v>
+      </c>
+      <c r="AG38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>9</v>
@@ -3953,69 +4389,81 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L39">
         <v>8</v>
       </c>
       <c r="M39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U39">
         <v>9</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC39">
         <v>9</v>
       </c>
-    </row>
-    <row r="40" spans="1:29">
+      <c r="AD39">
+        <v>7</v>
+      </c>
+      <c r="AE39">
+        <v>10</v>
+      </c>
+      <c r="AF39">
+        <v>9</v>
+      </c>
+      <c r="AG39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>8</v>
@@ -4039,72 +4487,84 @@
         <v>8</v>
       </c>
       <c r="I40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N40">
         <v>5</v>
       </c>
       <c r="O40">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>8</v>
       </c>
       <c r="S40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z40">
         <v>8</v>
       </c>
       <c r="AA40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB40">
         <v>7</v>
       </c>
       <c r="AC40">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD40">
+        <v>5</v>
+      </c>
+      <c r="AE40">
+        <v>7</v>
+      </c>
+      <c r="AF40">
+        <v>7</v>
+      </c>
+      <c r="AG40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -4128,7 +4588,7 @@
         <v>6</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J41">
         <v>5</v>
@@ -4137,49 +4597,49 @@
         <v>5</v>
       </c>
       <c r="L41">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M41">
+        <v>9</v>
+      </c>
+      <c r="N41">
         <v>4</v>
       </c>
-      <c r="N41">
-        <v>5</v>
-      </c>
       <c r="O41">
+        <v>5</v>
+      </c>
+      <c r="P41">
         <v>4</v>
       </c>
-      <c r="P41">
-        <v>8</v>
-      </c>
       <c r="Q41">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S41">
         <v>5</v>
       </c>
       <c r="T41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U41">
         <v>5</v>
       </c>
       <c r="V41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X41">
         <v>5</v>
       </c>
       <c r="Y41">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA41">
         <v>5</v>
@@ -4188,12 +4648,24 @@
         <v>5</v>
       </c>
       <c r="AC41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD41">
+        <v>5</v>
+      </c>
+      <c r="AE41">
+        <v>5</v>
+      </c>
+      <c r="AF41">
+        <v>5</v>
+      </c>
+      <c r="AG41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>9</v>
@@ -4220,69 +4692,81 @@
         <v>10</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L42">
         <v>8</v>
       </c>
       <c r="M42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O42">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P42">
         <v>9</v>
       </c>
       <c r="Q42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>9</v>
       </c>
       <c r="S42">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U42">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X42">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC42">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD42">
+        <v>10</v>
+      </c>
+      <c r="AE42">
+        <v>7</v>
+      </c>
+      <c r="AF42">
+        <v>9</v>
+      </c>
+      <c r="AG42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B43">
         <v>8</v>
@@ -4309,72 +4793,84 @@
         <v>10</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N43">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA43">
         <v>7</v>
       </c>
       <c r="AB43">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC43">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="AD43">
+        <v>7</v>
+      </c>
+      <c r="AE43">
+        <v>10</v>
+      </c>
+      <c r="AF43">
+        <v>7</v>
+      </c>
+      <c r="AG43">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="W1:AC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4382,16 +4878,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -4399,26 +4895,29 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4444,56 +4943,65 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Y2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -4520,20 +5028,20 @@
         <v>100</v>
       </c>
       <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
         <v>86.7</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>95.2</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>96.8</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>90</v>
       </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
       <c r="O4">
         <v>100</v>
       </c>
@@ -4541,27 +5049,36 @@
         <v>100</v>
       </c>
       <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
         <v>91.7</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>97</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>98</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>93.3</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>95.8</v>
       </c>
-      <c r="V4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="X4">
+        <v>100</v>
+      </c>
+      <c r="Y4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -4591,14 +5108,14 @@
         <v>100</v>
       </c>
       <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
         <v>95.2</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>93.5</v>
       </c>
-      <c r="M5">
-        <v>100</v>
-      </c>
       <c r="N5">
         <v>100</v>
       </c>
@@ -4612,24 +5129,33 @@
         <v>100</v>
       </c>
       <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
         <v>97</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>95.90000000000001</v>
       </c>
-      <c r="T5">
-        <v>100</v>
-      </c>
-      <c r="U5">
+      <c r="V5">
+        <v>100</v>
+      </c>
+      <c r="W5">
         <v>95.8</v>
       </c>
-      <c r="V5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="X5">
+        <v>100</v>
+      </c>
+      <c r="Y5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -4653,51 +5179,60 @@
         <v>100</v>
       </c>
       <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
         <v>95</v>
       </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
       <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
         <v>90.5</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>96.8</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>90</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>96.90000000000001</v>
       </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
       <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
         <v>90</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>93.8</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>92.40000000000001</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>95.90000000000001</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <v>88.3</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>91.7</v>
       </c>
-      <c r="V6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="X6">
+        <v>100</v>
+      </c>
+      <c r="Y6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>80</v>
@@ -4721,51 +5256,60 @@
         <v>100</v>
       </c>
       <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
         <v>85</v>
       </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
       <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="L7">
         <v>95.2</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>90.3</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>82.5</v>
       </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
         <v>90</v>
       </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
-      <c r="R7">
+      <c r="S7">
+        <v>100</v>
+      </c>
+      <c r="T7">
         <v>97</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>91.8</v>
       </c>
-      <c r="T7">
+      <c r="V7">
         <v>88.3</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>93.8</v>
       </c>
-      <c r="V7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="X7">
+        <v>100</v>
+      </c>
+      <c r="Y7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>90</v>
@@ -4789,51 +5333,60 @@
         <v>100</v>
       </c>
       <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
         <v>95</v>
       </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
       <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
         <v>92.90000000000001</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>96.8</v>
       </c>
-      <c r="M8">
-        <v>100</v>
-      </c>
       <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
         <v>96.90000000000001</v>
       </c>
-      <c r="O8">
-        <v>100</v>
-      </c>
       <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>96.7</v>
       </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
         <v>89.40000000000001</v>
       </c>
-      <c r="S8">
+      <c r="U8">
         <v>91.8</v>
       </c>
-      <c r="T8">
-        <v>100</v>
-      </c>
-      <c r="U8">
+      <c r="V8">
+        <v>100</v>
+      </c>
+      <c r="W8">
         <v>91.7</v>
       </c>
-      <c r="V8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="X8">
+        <v>100</v>
+      </c>
+      <c r="Y8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>90</v>
@@ -4857,51 +5410,60 @@
         <v>100</v>
       </c>
       <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
         <v>95</v>
       </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
       <c r="K9">
+        <v>100</v>
+      </c>
+      <c r="L9">
         <v>95.2</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>96.8</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>97.5</v>
       </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
+        <v>100</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
         <v>96.7</v>
       </c>
-      <c r="Q9">
-        <v>100</v>
-      </c>
-      <c r="R9">
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
         <v>95.5</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>95.90000000000001</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>98.3</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>95.8</v>
       </c>
-      <c r="V9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="X9">
+        <v>100</v>
+      </c>
+      <c r="Y9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>90</v>
@@ -4925,20 +5487,20 @@
         <v>100</v>
       </c>
       <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10">
         <v>95</v>
       </c>
-      <c r="J10">
-        <v>100</v>
-      </c>
       <c r="K10">
+        <v>100</v>
+      </c>
+      <c r="L10">
         <v>95.2</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>93.5</v>
       </c>
-      <c r="M10">
-        <v>100</v>
-      </c>
       <c r="N10">
         <v>100</v>
       </c>
@@ -4946,30 +5508,39 @@
         <v>100</v>
       </c>
       <c r="P10">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
         <v>96.7</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>97.90000000000001</v>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>97</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>93.90000000000001</v>
       </c>
-      <c r="T10">
-        <v>100</v>
-      </c>
-      <c r="U10">
+      <c r="V10">
+        <v>100</v>
+      </c>
+      <c r="W10">
         <v>95.8</v>
       </c>
-      <c r="V10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="X10">
+        <v>100</v>
+      </c>
+      <c r="Y10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -4999,14 +5570,14 @@
         <v>100</v>
       </c>
       <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
         <v>95.2</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>96.8</v>
       </c>
-      <c r="M11">
-        <v>100</v>
-      </c>
       <c r="N11">
         <v>100</v>
       </c>
@@ -5020,24 +5591,33 @@
         <v>100</v>
       </c>
       <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
         <v>97</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>98</v>
       </c>
-      <c r="T11">
-        <v>100</v>
-      </c>
-      <c r="U11">
+      <c r="V11">
+        <v>100</v>
+      </c>
+      <c r="W11">
         <v>95.8</v>
       </c>
-      <c r="V11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="X11">
+        <v>100</v>
+      </c>
+      <c r="Y11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -5067,14 +5647,14 @@
         <v>100</v>
       </c>
       <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
         <v>95.2</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>96.8</v>
       </c>
-      <c r="M12">
-        <v>100</v>
-      </c>
       <c r="N12">
         <v>100</v>
       </c>
@@ -5088,24 +5668,33 @@
         <v>100</v>
       </c>
       <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>97</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>98</v>
       </c>
-      <c r="T12">
-        <v>100</v>
-      </c>
-      <c r="U12">
+      <c r="V12">
+        <v>100</v>
+      </c>
+      <c r="W12">
         <v>97.90000000000001</v>
       </c>
-      <c r="V12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="X12">
+        <v>100</v>
+      </c>
+      <c r="Y12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>90</v>
@@ -5129,20 +5718,20 @@
         <v>100</v>
       </c>
       <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
         <v>90</v>
       </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
       <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
         <v>92.90000000000001</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>96.8</v>
       </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
       <c r="N13">
         <v>100</v>
       </c>
@@ -5150,30 +5739,39 @@
         <v>100</v>
       </c>
       <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>93.3</v>
       </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
+      <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
         <v>95.5</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>98</v>
       </c>
-      <c r="T13">
-        <v>100</v>
-      </c>
-      <c r="U13">
+      <c r="V13">
+        <v>100</v>
+      </c>
+      <c r="W13">
         <v>97.90000000000001</v>
       </c>
-      <c r="V13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="X13">
+        <v>100</v>
+      </c>
+      <c r="Y13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -5203,14 +5801,14 @@
         <v>100</v>
       </c>
       <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
         <v>95.2</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>96.8</v>
       </c>
-      <c r="M14">
-        <v>100</v>
-      </c>
       <c r="N14">
         <v>100</v>
       </c>
@@ -5224,24 +5822,33 @@
         <v>100</v>
       </c>
       <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
         <v>97</v>
       </c>
-      <c r="S14">
+      <c r="U14">
         <v>98</v>
       </c>
-      <c r="T14">
-        <v>100</v>
-      </c>
-      <c r="U14">
+      <c r="V14">
+        <v>100</v>
+      </c>
+      <c r="W14">
         <v>97.90000000000001</v>
       </c>
-      <c r="V14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="X14">
+        <v>100</v>
+      </c>
+      <c r="Y14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -5271,14 +5878,14 @@
         <v>100</v>
       </c>
       <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
         <v>95.2</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>96.8</v>
       </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
       <c r="N15">
         <v>100</v>
       </c>
@@ -5292,24 +5899,33 @@
         <v>100</v>
       </c>
       <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
         <v>97</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>98</v>
       </c>
-      <c r="T15">
-        <v>100</v>
-      </c>
-      <c r="U15">
+      <c r="V15">
+        <v>100</v>
+      </c>
+      <c r="W15">
         <v>97.90000000000001</v>
       </c>
-      <c r="V15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="X15">
+        <v>100</v>
+      </c>
+      <c r="Y15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>100</v>
@@ -5336,17 +5952,17 @@
         <v>100</v>
       </c>
       <c r="J16">
+        <v>100</v>
+      </c>
+      <c r="K16">
         <v>96.7</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>95.2</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>96.8</v>
       </c>
-      <c r="M16">
-        <v>100</v>
-      </c>
       <c r="N16">
         <v>100</v>
       </c>
@@ -5357,27 +5973,36 @@
         <v>100</v>
       </c>
       <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
         <v>97.90000000000001</v>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>97</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>98</v>
       </c>
-      <c r="T16">
-        <v>100</v>
-      </c>
-      <c r="U16">
+      <c r="V16">
+        <v>100</v>
+      </c>
+      <c r="W16">
         <v>97.90000000000001</v>
       </c>
-      <c r="V16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="X16">
+        <v>100</v>
+      </c>
+      <c r="Y16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -5407,14 +6032,14 @@
         <v>100</v>
       </c>
       <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
         <v>95.2</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>96.8</v>
       </c>
-      <c r="M17">
-        <v>100</v>
-      </c>
       <c r="N17">
         <v>100</v>
       </c>
@@ -5428,24 +6053,33 @@
         <v>100</v>
       </c>
       <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
         <v>97</v>
       </c>
-      <c r="S17">
+      <c r="U17">
         <v>98</v>
       </c>
-      <c r="T17">
-        <v>100</v>
-      </c>
-      <c r="U17">
-        <v>100</v>
-      </c>
       <c r="V17">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="W17">
+        <v>100</v>
+      </c>
+      <c r="X17">
+        <v>100</v>
+      </c>
+      <c r="Y17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -5469,20 +6103,20 @@
         <v>100</v>
       </c>
       <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
         <v>95</v>
       </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
         <v>90.5</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>96.8</v>
       </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
       <c r="N18">
         <v>100</v>
       </c>
@@ -5490,30 +6124,39 @@
         <v>100</v>
       </c>
       <c r="P18">
+        <v>100</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>93.3</v>
       </c>
-      <c r="Q18">
+      <c r="S18">
         <v>97.90000000000001</v>
       </c>
-      <c r="R18">
+      <c r="T18">
         <v>92.40000000000001</v>
       </c>
-      <c r="S18">
+      <c r="U18">
         <v>95.90000000000001</v>
       </c>
-      <c r="T18">
-        <v>100</v>
-      </c>
-      <c r="U18">
+      <c r="V18">
+        <v>100</v>
+      </c>
+      <c r="W18">
         <v>97.90000000000001</v>
       </c>
-      <c r="V18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="X18">
+        <v>100</v>
+      </c>
+      <c r="Y18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>90</v>
@@ -5537,51 +6180,60 @@
         <v>100</v>
       </c>
       <c r="I19">
+        <v>100</v>
+      </c>
+      <c r="J19">
         <v>90</v>
       </c>
-      <c r="J19">
-        <v>100</v>
-      </c>
       <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
         <v>85.7</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>83.90000000000001</v>
       </c>
-      <c r="M19">
-        <v>100</v>
-      </c>
       <c r="N19">
+        <v>100</v>
+      </c>
+      <c r="O19">
         <v>90.59999999999999</v>
       </c>
-      <c r="O19">
-        <v>100</v>
-      </c>
       <c r="P19">
+        <v>100</v>
+      </c>
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
         <v>93.3</v>
       </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
-      <c r="R19">
+      <c r="S19">
+        <v>100</v>
+      </c>
+      <c r="T19">
         <v>90.90000000000001</v>
       </c>
-      <c r="S19">
+      <c r="U19">
         <v>89.8</v>
       </c>
-      <c r="T19">
-        <v>100</v>
-      </c>
-      <c r="U19">
+      <c r="V19">
+        <v>100</v>
+      </c>
+      <c r="W19">
         <v>91.7</v>
       </c>
-      <c r="V19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="X19">
+        <v>100</v>
+      </c>
+      <c r="Y19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>80</v>
@@ -5605,51 +6257,60 @@
         <v>100</v>
       </c>
       <c r="I20">
+        <v>100</v>
+      </c>
+      <c r="J20">
         <v>90</v>
       </c>
-      <c r="J20">
-        <v>100</v>
-      </c>
       <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="L20">
         <v>92.90000000000001</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>87.09999999999999</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>92.5</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>93.8</v>
       </c>
-      <c r="O20">
-        <v>100</v>
-      </c>
       <c r="P20">
+        <v>100</v>
+      </c>
+      <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
         <v>86.7</v>
       </c>
-      <c r="Q20">
+      <c r="S20">
         <v>89.59999999999999</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>95.5</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>91.8</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>91.7</v>
       </c>
-      <c r="U20">
+      <c r="W20">
         <v>87.5</v>
       </c>
-      <c r="V20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="X20">
+        <v>100</v>
+      </c>
+      <c r="Y20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -5679,14 +6340,14 @@
         <v>100</v>
       </c>
       <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
         <v>95.2</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>96.8</v>
       </c>
-      <c r="M21">
-        <v>100</v>
-      </c>
       <c r="N21">
         <v>100</v>
       </c>
@@ -5700,24 +6361,33 @@
         <v>100</v>
       </c>
       <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
         <v>95.5</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>95.90000000000001</v>
       </c>
-      <c r="T21">
-        <v>100</v>
-      </c>
-      <c r="U21">
-        <v>100</v>
-      </c>
       <c r="V21">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="W21">
+        <v>100</v>
+      </c>
+      <c r="X21">
+        <v>100</v>
+      </c>
+      <c r="Y21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>80</v>
@@ -5741,51 +6411,60 @@
         <v>100</v>
       </c>
       <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22">
         <v>85</v>
       </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
       <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
         <v>88.09999999999999</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>93.5</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>92.5</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>90.59999999999999</v>
       </c>
-      <c r="O22">
-        <v>100</v>
-      </c>
       <c r="P22">
+        <v>100</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>86.7</v>
       </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
         <v>92.40000000000001</v>
       </c>
-      <c r="S22">
+      <c r="U22">
         <v>95.90000000000001</v>
       </c>
-      <c r="T22">
+      <c r="V22">
         <v>91.7</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>87.5</v>
       </c>
-      <c r="V22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="X22">
+        <v>100</v>
+      </c>
+      <c r="Y22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>80</v>
@@ -5809,51 +6488,60 @@
         <v>100</v>
       </c>
       <c r="I23">
+        <v>100</v>
+      </c>
+      <c r="J23">
         <v>65</v>
       </c>
-      <c r="J23">
-        <v>100</v>
-      </c>
       <c r="K23">
+        <v>100</v>
+      </c>
+      <c r="L23">
         <v>83.3</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>83.90000000000001</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>90</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>78.09999999999999</v>
       </c>
-      <c r="O23">
-        <v>100</v>
-      </c>
       <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
+        <v>50</v>
+      </c>
+      <c r="R23">
         <v>43.3</v>
       </c>
-      <c r="Q23">
+      <c r="S23">
         <v>62.5</v>
       </c>
-      <c r="R23">
+      <c r="T23">
         <v>53</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>53.1</v>
       </c>
-      <c r="T23">
+      <c r="V23">
         <v>60</v>
       </c>
-      <c r="U23">
+      <c r="W23">
         <v>54.2</v>
       </c>
-      <c r="V23">
+      <c r="X23">
         <v>61.5</v>
       </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="Y23">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>80</v>
@@ -5877,51 +6565,60 @@
         <v>100</v>
       </c>
       <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24">
         <v>80</v>
       </c>
-      <c r="J24">
-        <v>100</v>
-      </c>
       <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
         <v>81</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>90.3</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>90</v>
       </c>
-      <c r="N24">
-        <v>100</v>
-      </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
+        <v>100</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>80</v>
       </c>
-      <c r="Q24">
+      <c r="S24">
         <v>93.8</v>
       </c>
-      <c r="R24">
+      <c r="T24">
         <v>86.40000000000001</v>
       </c>
-      <c r="S24">
+      <c r="U24">
         <v>89.8</v>
       </c>
-      <c r="T24">
+      <c r="V24">
         <v>91.7</v>
       </c>
-      <c r="U24">
+      <c r="W24">
         <v>93.8</v>
       </c>
-      <c r="V24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="X24">
+        <v>100</v>
+      </c>
+      <c r="Y24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -5951,14 +6648,14 @@
         <v>100</v>
       </c>
       <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
         <v>95.2</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>96.8</v>
       </c>
-      <c r="M25">
-        <v>100</v>
-      </c>
       <c r="N25">
         <v>100</v>
       </c>
@@ -5972,24 +6669,33 @@
         <v>100</v>
       </c>
       <c r="R25">
+        <v>100</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+      <c r="T25">
         <v>97</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>98</v>
       </c>
-      <c r="T25">
-        <v>100</v>
-      </c>
-      <c r="U25">
+      <c r="V25">
+        <v>100</v>
+      </c>
+      <c r="W25">
         <v>93.8</v>
       </c>
-      <c r="V25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="X25">
+        <v>100</v>
+      </c>
+      <c r="Y25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -6016,48 +6722,57 @@
         <v>100</v>
       </c>
       <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
         <v>86.7</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>95.2</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>96.8</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>97.5</v>
       </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
       <c r="O26">
         <v>100</v>
       </c>
       <c r="P26">
+        <v>100</v>
+      </c>
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>96.7</v>
       </c>
-      <c r="Q26">
+      <c r="S26">
         <v>91.7</v>
       </c>
-      <c r="R26">
+      <c r="T26">
         <v>97</v>
       </c>
-      <c r="S26">
+      <c r="U26">
         <v>98</v>
       </c>
-      <c r="T26">
+      <c r="V26">
         <v>98.3</v>
       </c>
-      <c r="U26">
+      <c r="W26">
         <v>97.90000000000001</v>
       </c>
-      <c r="V26">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="X26">
+        <v>100</v>
+      </c>
+      <c r="Y26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -6081,51 +6796,60 @@
         <v>100</v>
       </c>
       <c r="I27">
+        <v>100</v>
+      </c>
+      <c r="J27">
         <v>95</v>
       </c>
-      <c r="J27">
-        <v>100</v>
-      </c>
       <c r="K27">
+        <v>100</v>
+      </c>
+      <c r="L27">
         <v>95.2</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>90.3</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>95</v>
       </c>
-      <c r="N27">
-        <v>100</v>
-      </c>
       <c r="O27">
         <v>100</v>
       </c>
       <c r="P27">
+        <v>100</v>
+      </c>
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>93.3</v>
       </c>
-      <c r="Q27">
-        <v>100</v>
-      </c>
-      <c r="R27">
+      <c r="S27">
+        <v>100</v>
+      </c>
+      <c r="T27">
         <v>95.5</v>
       </c>
-      <c r="S27">
+      <c r="U27">
         <v>91.8</v>
       </c>
-      <c r="T27">
+      <c r="V27">
         <v>96.7</v>
       </c>
-      <c r="U27">
-        <v>100</v>
-      </c>
-      <c r="V27">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="W27">
+        <v>100</v>
+      </c>
+      <c r="X27">
+        <v>100</v>
+      </c>
+      <c r="Y27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -6155,20 +6879,20 @@
         <v>100</v>
       </c>
       <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
         <v>85.7</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>96.8</v>
       </c>
-      <c r="M28">
-        <v>100</v>
-      </c>
       <c r="N28">
+        <v>100</v>
+      </c>
+      <c r="O28">
         <v>96.90000000000001</v>
       </c>
-      <c r="O28">
-        <v>100</v>
-      </c>
       <c r="P28">
         <v>100</v>
       </c>
@@ -6176,24 +6900,33 @@
         <v>100</v>
       </c>
       <c r="R28">
+        <v>100</v>
+      </c>
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
         <v>87.90000000000001</v>
       </c>
-      <c r="S28">
+      <c r="U28">
         <v>95.90000000000001</v>
       </c>
-      <c r="T28">
-        <v>100</v>
-      </c>
-      <c r="U28">
+      <c r="V28">
+        <v>100</v>
+      </c>
+      <c r="W28">
         <v>95.8</v>
       </c>
-      <c r="V28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="X28">
+        <v>100</v>
+      </c>
+      <c r="Y28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -6223,20 +6956,20 @@
         <v>100</v>
       </c>
       <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
         <v>95.2</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>96.8</v>
       </c>
-      <c r="M29">
-        <v>100</v>
-      </c>
       <c r="N29">
+        <v>100</v>
+      </c>
+      <c r="O29">
         <v>96.90000000000001</v>
       </c>
-      <c r="O29">
-        <v>100</v>
-      </c>
       <c r="P29">
         <v>100</v>
       </c>
@@ -6244,24 +6977,33 @@
         <v>100</v>
       </c>
       <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
         <v>97</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>98</v>
       </c>
-      <c r="T29">
-        <v>100</v>
-      </c>
-      <c r="U29">
+      <c r="V29">
+        <v>100</v>
+      </c>
+      <c r="W29">
         <v>97.90000000000001</v>
       </c>
-      <c r="V29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="X29">
+        <v>100</v>
+      </c>
+      <c r="Y29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>90</v>
@@ -6285,20 +7027,20 @@
         <v>100</v>
       </c>
       <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
         <v>95</v>
       </c>
-      <c r="J30">
-        <v>100</v>
-      </c>
       <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
         <v>95.2</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>93.5</v>
       </c>
-      <c r="M30">
-        <v>100</v>
-      </c>
       <c r="N30">
         <v>100</v>
       </c>
@@ -6306,30 +7048,39 @@
         <v>100</v>
       </c>
       <c r="P30">
+        <v>100</v>
+      </c>
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
         <v>96.7</v>
       </c>
-      <c r="Q30">
-        <v>100</v>
-      </c>
-      <c r="R30">
+      <c r="S30">
+        <v>100</v>
+      </c>
+      <c r="T30">
         <v>97</v>
       </c>
-      <c r="S30">
+      <c r="U30">
         <v>95.90000000000001</v>
       </c>
-      <c r="T30">
-        <v>100</v>
-      </c>
-      <c r="U30">
+      <c r="V30">
+        <v>100</v>
+      </c>
+      <c r="W30">
         <v>93.8</v>
       </c>
-      <c r="V30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+      <c r="X30">
+        <v>100</v>
+      </c>
+      <c r="Y30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -6359,20 +7110,20 @@
         <v>100</v>
       </c>
       <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
         <v>95.2</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>96.8</v>
       </c>
-      <c r="M31">
-        <v>100</v>
-      </c>
       <c r="N31">
+        <v>100</v>
+      </c>
+      <c r="O31">
         <v>93.8</v>
       </c>
-      <c r="O31">
-        <v>100</v>
-      </c>
       <c r="P31">
         <v>100</v>
       </c>
@@ -6380,24 +7131,33 @@
         <v>100</v>
       </c>
       <c r="R31">
+        <v>100</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
         <v>97</v>
       </c>
-      <c r="S31">
+      <c r="U31">
         <v>98</v>
       </c>
-      <c r="T31">
-        <v>100</v>
-      </c>
-      <c r="U31">
+      <c r="V31">
+        <v>100</v>
+      </c>
+      <c r="W31">
         <v>89.59999999999999</v>
       </c>
-      <c r="V31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="X31">
+        <v>100</v>
+      </c>
+      <c r="Y31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>100</v>
@@ -6427,45 +7187,54 @@
         <v>100</v>
       </c>
       <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
         <v>95.2</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>93.5</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>90</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>93.8</v>
       </c>
-      <c r="O32">
-        <v>100</v>
-      </c>
       <c r="P32">
         <v>100</v>
       </c>
       <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
+        <v>100</v>
+      </c>
+      <c r="S32">
         <v>97.90000000000001</v>
       </c>
-      <c r="R32">
+      <c r="T32">
         <v>97</v>
       </c>
-      <c r="S32">
+      <c r="U32">
         <v>93.90000000000001</v>
       </c>
-      <c r="T32">
+      <c r="V32">
         <v>93.3</v>
       </c>
-      <c r="U32">
+      <c r="W32">
         <v>89.59999999999999</v>
       </c>
-      <c r="V32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="X32">
+        <v>100</v>
+      </c>
+      <c r="Y32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>90</v>
@@ -6489,11 +7258,11 @@
         <v>90</v>
       </c>
       <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
         <v>95</v>
       </c>
-      <c r="J33">
-        <v>100</v>
-      </c>
       <c r="K33">
         <v>100</v>
       </c>
@@ -6501,39 +7270,48 @@
         <v>100</v>
       </c>
       <c r="M33">
+        <v>100</v>
+      </c>
+      <c r="N33">
         <v>90</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>93.8</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>95</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
         <v>96.7</v>
       </c>
-      <c r="Q33">
+      <c r="S33">
         <v>93.8</v>
       </c>
-      <c r="R33">
-        <v>100</v>
-      </c>
-      <c r="S33">
-        <v>100</v>
-      </c>
       <c r="T33">
+        <v>100</v>
+      </c>
+      <c r="U33">
+        <v>100</v>
+      </c>
+      <c r="V33">
         <v>93.3</v>
       </c>
-      <c r="U33">
+      <c r="W33">
         <v>95.8</v>
       </c>
-      <c r="V33">
+      <c r="X33">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="Y33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>100</v>
@@ -6563,20 +7341,20 @@
         <v>100</v>
       </c>
       <c r="K34">
+        <v>100</v>
+      </c>
+      <c r="L34">
         <v>95.2</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>96.8</v>
       </c>
-      <c r="M34">
-        <v>100</v>
-      </c>
       <c r="N34">
+        <v>100</v>
+      </c>
+      <c r="O34">
         <v>96.90000000000001</v>
       </c>
-      <c r="O34">
-        <v>100</v>
-      </c>
       <c r="P34">
         <v>100</v>
       </c>
@@ -6584,24 +7362,33 @@
         <v>100</v>
       </c>
       <c r="R34">
+        <v>100</v>
+      </c>
+      <c r="S34">
+        <v>100</v>
+      </c>
+      <c r="T34">
         <v>97</v>
       </c>
-      <c r="S34">
+      <c r="U34">
         <v>98</v>
       </c>
-      <c r="T34">
-        <v>100</v>
-      </c>
-      <c r="U34">
+      <c r="V34">
+        <v>100</v>
+      </c>
+      <c r="W34">
         <v>97.90000000000001</v>
       </c>
-      <c r="V34">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22">
+      <c r="X34">
+        <v>100</v>
+      </c>
+      <c r="Y34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>100</v>
@@ -6631,14 +7418,14 @@
         <v>100</v>
       </c>
       <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
         <v>92.90000000000001</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>96.8</v>
       </c>
-      <c r="M35">
-        <v>100</v>
-      </c>
       <c r="N35">
         <v>100</v>
       </c>
@@ -6652,24 +7439,33 @@
         <v>100</v>
       </c>
       <c r="R35">
+        <v>100</v>
+      </c>
+      <c r="S35">
+        <v>100</v>
+      </c>
+      <c r="T35">
         <v>95.5</v>
       </c>
-      <c r="S35">
+      <c r="U35">
         <v>98</v>
       </c>
-      <c r="T35">
-        <v>100</v>
-      </c>
-      <c r="U35">
-        <v>100</v>
-      </c>
       <c r="V35">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="1:22">
+      <c r="W35">
+        <v>100</v>
+      </c>
+      <c r="X35">
+        <v>100</v>
+      </c>
+      <c r="Y35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>100</v>
@@ -6699,14 +7495,14 @@
         <v>100</v>
       </c>
       <c r="K36">
+        <v>100</v>
+      </c>
+      <c r="L36">
         <v>90.5</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>96.8</v>
       </c>
-      <c r="M36">
-        <v>100</v>
-      </c>
       <c r="N36">
         <v>100</v>
       </c>
@@ -6720,24 +7516,33 @@
         <v>100</v>
       </c>
       <c r="R36">
+        <v>100</v>
+      </c>
+      <c r="S36">
+        <v>100</v>
+      </c>
+      <c r="T36">
         <v>93.90000000000001</v>
       </c>
-      <c r="S36">
+      <c r="U36">
         <v>98</v>
       </c>
-      <c r="T36">
-        <v>100</v>
-      </c>
-      <c r="U36">
-        <v>100</v>
-      </c>
       <c r="V36">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="1:22">
+      <c r="W36">
+        <v>100</v>
+      </c>
+      <c r="X36">
+        <v>100</v>
+      </c>
+      <c r="Y36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>100</v>
@@ -6767,14 +7572,14 @@
         <v>100</v>
       </c>
       <c r="K37">
+        <v>100</v>
+      </c>
+      <c r="L37">
         <v>92.90000000000001</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>96.8</v>
       </c>
-      <c r="M37">
-        <v>100</v>
-      </c>
       <c r="N37">
         <v>100</v>
       </c>
@@ -6788,24 +7593,33 @@
         <v>100</v>
       </c>
       <c r="R37">
+        <v>100</v>
+      </c>
+      <c r="S37">
+        <v>100</v>
+      </c>
+      <c r="T37">
         <v>95.5</v>
       </c>
-      <c r="S37">
+      <c r="U37">
         <v>98</v>
       </c>
-      <c r="T37">
-        <v>100</v>
-      </c>
-      <c r="U37">
-        <v>100</v>
-      </c>
       <c r="V37">
         <v>100</v>
       </c>
-    </row>
-    <row r="38" spans="1:22">
+      <c r="W37">
+        <v>100</v>
+      </c>
+      <c r="X37">
+        <v>100</v>
+      </c>
+      <c r="Y37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38">
         <v>100</v>
@@ -6835,14 +7649,14 @@
         <v>100</v>
       </c>
       <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
         <v>95.2</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>96.8</v>
       </c>
-      <c r="M38">
-        <v>100</v>
-      </c>
       <c r="N38">
         <v>100</v>
       </c>
@@ -6856,24 +7670,33 @@
         <v>100</v>
       </c>
       <c r="R38">
+        <v>100</v>
+      </c>
+      <c r="S38">
+        <v>100</v>
+      </c>
+      <c r="T38">
         <v>97</v>
       </c>
-      <c r="S38">
+      <c r="U38">
         <v>98</v>
       </c>
-      <c r="T38">
-        <v>100</v>
-      </c>
-      <c r="U38">
-        <v>100</v>
-      </c>
       <c r="V38">
         <v>100</v>
       </c>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="W38">
+        <v>100</v>
+      </c>
+      <c r="X38">
+        <v>100</v>
+      </c>
+      <c r="Y38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
       <c r="A39" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>100</v>
@@ -6903,20 +7726,20 @@
         <v>100</v>
       </c>
       <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
         <v>90.5</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>93.5</v>
       </c>
-      <c r="M39">
-        <v>100</v>
-      </c>
       <c r="N39">
+        <v>100</v>
+      </c>
+      <c r="O39">
         <v>93.8</v>
       </c>
-      <c r="O39">
-        <v>100</v>
-      </c>
       <c r="P39">
         <v>100</v>
       </c>
@@ -6924,24 +7747,33 @@
         <v>100</v>
       </c>
       <c r="R39">
+        <v>100</v>
+      </c>
+      <c r="S39">
+        <v>100</v>
+      </c>
+      <c r="T39">
         <v>92.40000000000001</v>
       </c>
-      <c r="S39">
+      <c r="U39">
         <v>95.90000000000001</v>
       </c>
-      <c r="T39">
-        <v>100</v>
-      </c>
-      <c r="U39">
+      <c r="V39">
+        <v>100</v>
+      </c>
+      <c r="W39">
         <v>93.8</v>
       </c>
-      <c r="V39">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22">
+      <c r="X39">
+        <v>100</v>
+      </c>
+      <c r="Y39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40">
         <v>100</v>
@@ -6965,51 +7797,60 @@
         <v>100</v>
       </c>
       <c r="I40">
+        <v>100</v>
+      </c>
+      <c r="J40">
         <v>95</v>
       </c>
-      <c r="J40">
-        <v>100</v>
-      </c>
       <c r="K40">
+        <v>100</v>
+      </c>
+      <c r="L40">
         <v>92.90000000000001</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>93.5</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>90</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>93.8</v>
       </c>
-      <c r="O40">
-        <v>100</v>
-      </c>
       <c r="P40">
+        <v>100</v>
+      </c>
+      <c r="Q40">
+        <v>100</v>
+      </c>
+      <c r="R40">
         <v>93.3</v>
       </c>
-      <c r="Q40">
-        <v>100</v>
-      </c>
-      <c r="R40">
+      <c r="S40">
+        <v>100</v>
+      </c>
+      <c r="T40">
         <v>95.5</v>
       </c>
-      <c r="S40">
+      <c r="U40">
         <v>95.90000000000001</v>
       </c>
-      <c r="T40">
+      <c r="V40">
         <v>90</v>
       </c>
-      <c r="U40">
+      <c r="W40">
         <v>93.8</v>
       </c>
-      <c r="V40">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22">
+      <c r="X40">
+        <v>100</v>
+      </c>
+      <c r="Y40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
       <c r="A41" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41">
         <v>80</v>
@@ -7033,51 +7874,60 @@
         <v>100</v>
       </c>
       <c r="I41">
+        <v>100</v>
+      </c>
+      <c r="J41">
         <v>80</v>
       </c>
-      <c r="J41">
-        <v>100</v>
-      </c>
       <c r="K41">
+        <v>100</v>
+      </c>
+      <c r="L41">
         <v>92.90000000000001</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>93.5</v>
       </c>
-      <c r="M41">
-        <v>100</v>
-      </c>
       <c r="N41">
+        <v>100</v>
+      </c>
+      <c r="O41">
         <v>68.8</v>
       </c>
-      <c r="O41">
-        <v>100</v>
-      </c>
       <c r="P41">
+        <v>100</v>
+      </c>
+      <c r="Q41">
+        <v>100</v>
+      </c>
+      <c r="R41">
         <v>86.7</v>
       </c>
-      <c r="Q41">
+      <c r="S41">
         <v>93.8</v>
       </c>
-      <c r="R41">
+      <c r="T41">
         <v>95.5</v>
       </c>
-      <c r="S41">
+      <c r="U41">
         <v>91.8</v>
       </c>
-      <c r="T41">
-        <v>100</v>
-      </c>
-      <c r="U41">
+      <c r="V41">
+        <v>100</v>
+      </c>
+      <c r="W41">
         <v>56.3</v>
       </c>
-      <c r="V41">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22">
+      <c r="X41">
+        <v>100</v>
+      </c>
+      <c r="Y41">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42">
         <v>100</v>
@@ -7107,14 +7957,14 @@
         <v>100</v>
       </c>
       <c r="K42">
+        <v>100</v>
+      </c>
+      <c r="L42">
         <v>90.5</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>96.8</v>
       </c>
-      <c r="M42">
-        <v>100</v>
-      </c>
       <c r="N42">
         <v>100</v>
       </c>
@@ -7125,27 +7975,36 @@
         <v>100</v>
       </c>
       <c r="Q42">
+        <v>100</v>
+      </c>
+      <c r="R42">
+        <v>100</v>
+      </c>
+      <c r="S42">
         <v>97.90000000000001</v>
       </c>
-      <c r="R42">
+      <c r="T42">
         <v>93.90000000000001</v>
       </c>
-      <c r="S42">
+      <c r="U42">
         <v>98</v>
       </c>
-      <c r="T42">
-        <v>100</v>
-      </c>
-      <c r="U42">
+      <c r="V42">
+        <v>100</v>
+      </c>
+      <c r="W42">
         <v>91.7</v>
       </c>
-      <c r="V42">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22">
+      <c r="X42">
+        <v>100</v>
+      </c>
+      <c r="Y42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B43">
         <v>100</v>
@@ -7175,14 +8034,14 @@
         <v>100</v>
       </c>
       <c r="K43">
+        <v>100</v>
+      </c>
+      <c r="L43">
         <v>95.2</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>93.5</v>
       </c>
-      <c r="M43">
-        <v>100</v>
-      </c>
       <c r="N43">
         <v>100</v>
       </c>
@@ -7196,26 +8055,35 @@
         <v>100</v>
       </c>
       <c r="R43">
+        <v>100</v>
+      </c>
+      <c r="S43">
+        <v>100</v>
+      </c>
+      <c r="T43">
         <v>97</v>
       </c>
-      <c r="S43">
+      <c r="U43">
         <v>95.90000000000001</v>
       </c>
-      <c r="T43">
-        <v>100</v>
-      </c>
-      <c r="U43">
-        <v>100</v>
-      </c>
       <c r="V43">
+        <v>100</v>
+      </c>
+      <c r="W43">
+        <v>100</v>
+      </c>
+      <c r="X43">
+        <v>100</v>
+      </c>
+      <c r="Y43">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7236,31 +8104,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -7425,28 +8293,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>40</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="G7" s="2">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7457,10 +8325,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8">
         <v>40</v>
@@ -7478,7 +8346,7 @@
         <v>2.5</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7489,21 +8357,33 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C9">
+        <v>40</v>
+      </c>
+      <c r="D9">
+        <v>39</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>97.5</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="H9">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="I9">
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -7538,7 +8418,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -7572,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>

--- a/grupos/1DM - Estadisticos 20231.xlsx
+++ b/grupos/1DM - Estadisticos 20231.xlsx
@@ -902,25 +902,25 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -1006,22 +1006,22 @@
         <v>10</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC5">
         <v>10</v>
       </c>
       <c r="AD5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1104,25 +1104,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD6">
         <v>5</v>
       </c>
       <c r="AE6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1205,25 +1205,25 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1306,25 +1306,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1407,25 +1407,25 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1508,25 +1508,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1609,25 +1609,25 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD11">
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1713,22 +1713,22 @@
         <v>10</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1811,25 +1811,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1915,22 +1915,22 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE14">
         <v>10</v>
       </c>
       <c r="AF14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -2013,25 +2013,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2117,22 +2117,22 @@
         <v>10</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC16">
         <v>10</v>
       </c>
       <c r="AD16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2218,22 +2218,22 @@
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2316,25 +2316,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2417,25 +2417,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2518,7 +2518,7 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA20">
         <v>5</v>
@@ -2527,13 +2527,13 @@
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD20">
         <v>5</v>
       </c>
       <c r="AE20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF20">
         <v>5</v>
@@ -2619,25 +2619,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2720,25 +2720,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2922,25 +2922,25 @@
         <v>10</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA24">
         <v>5</v>
       </c>
       <c r="AB24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD24">
         <v>5</v>
       </c>
       <c r="AE24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -3026,22 +3026,22 @@
         <v>10</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3124,25 +3124,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE26">
         <v>10</v>
       </c>
       <c r="AF26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3225,25 +3225,25 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3326,25 +3326,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3427,25 +3427,25 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>10</v>
       </c>
       <c r="AD29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE29">
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3528,25 +3528,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3629,25 +3629,25 @@
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD31">
         <v>5</v>
       </c>
       <c r="AE31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3730,25 +3730,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD32">
         <v>5</v>
       </c>
       <c r="AE32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3831,25 +3831,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD33">
         <v>5</v>
       </c>
       <c r="AE33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -3935,7 +3935,7 @@
         <v>10</v>
       </c>
       <c r="AA34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB34">
         <v>10</v>
@@ -3944,13 +3944,13 @@
         <v>10</v>
       </c>
       <c r="AD34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE34">
         <v>10</v>
       </c>
       <c r="AF34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG34">
         <v>10</v>
@@ -4033,25 +4033,25 @@
         <v>10</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE35">
         <v>10</v>
       </c>
       <c r="AF35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4137,22 +4137,22 @@
         <v>10</v>
       </c>
       <c r="AA36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC36">
         <v>10</v>
       </c>
       <c r="AD36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE36">
         <v>10</v>
       </c>
       <c r="AF36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG36">
         <v>10</v>
@@ -4238,16 +4238,16 @@
         <v>10</v>
       </c>
       <c r="AA37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC37">
         <v>10</v>
       </c>
       <c r="AD37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE37">
         <v>10</v>
@@ -4339,22 +4339,22 @@
         <v>10</v>
       </c>
       <c r="AA38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE38">
         <v>10</v>
       </c>
       <c r="AF38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG38">
         <v>10</v>
@@ -4440,22 +4440,22 @@
         <v>10</v>
       </c>
       <c r="AA39">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE39">
         <v>10</v>
       </c>
       <c r="AF39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG39">
         <v>10</v>
@@ -4538,25 +4538,25 @@
         <v>10</v>
       </c>
       <c r="Z40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD40">
         <v>5</v>
       </c>
       <c r="AE40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF40">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG40">
         <v>10</v>
@@ -4639,7 +4639,7 @@
         <v>10</v>
       </c>
       <c r="Z41">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA41">
         <v>5</v>
@@ -4648,7 +4648,7 @@
         <v>5</v>
       </c>
       <c r="AC41">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD41">
         <v>5</v>
@@ -4740,25 +4740,25 @@
         <v>10</v>
       </c>
       <c r="Z42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA42">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD42">
         <v>10</v>
       </c>
       <c r="AE42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG42">
         <v>10</v>
@@ -4841,25 +4841,25 @@
         <v>10</v>
       </c>
       <c r="Z43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB43">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC43">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE43">
         <v>10</v>
       </c>
       <c r="AF43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG43">
         <v>10</v>
@@ -8154,7 +8154,7 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -8186,7 +8186,7 @@
         <v>10</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8218,7 +8218,7 @@
         <v>7.5</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8250,7 +8250,7 @@
         <v>7.5</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8282,7 +8282,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8346,7 +8346,7 @@
         <v>2.5</v>
       </c>
       <c r="H8">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8378,7 +8378,7 @@
         <v>2.5</v>
       </c>
       <c r="H9">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="I9">
         <v>0</v>

--- a/grupos/1DM - Estadisticos 20231.xlsx
+++ b/grupos/1DM - Estadisticos 20231.xlsx
@@ -902,25 +902,25 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -1006,22 +1006,22 @@
         <v>10</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>10</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1104,25 +1104,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD6">
         <v>5</v>
       </c>
       <c r="AE6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1205,25 +1205,25 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1306,25 +1306,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1407,25 +1407,25 @@
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -1508,25 +1508,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1609,25 +1609,25 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD11">
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1713,22 +1713,22 @@
         <v>10</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1811,25 +1811,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1915,22 +1915,22 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE14">
         <v>10</v>
       </c>
       <c r="AF14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -2013,25 +2013,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2117,22 +2117,22 @@
         <v>10</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>10</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2218,22 +2218,22 @@
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2316,25 +2316,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2417,25 +2417,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2518,7 +2518,7 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>5</v>
@@ -2527,13 +2527,13 @@
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD20">
         <v>5</v>
       </c>
       <c r="AE20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF20">
         <v>5</v>
@@ -2619,25 +2619,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2720,25 +2720,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2922,25 +2922,25 @@
         <v>10</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>5</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD24">
         <v>5</v>
       </c>
       <c r="AE24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -3026,22 +3026,22 @@
         <v>10</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3124,25 +3124,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE26">
         <v>10</v>
       </c>
       <c r="AF26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3225,25 +3225,25 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3326,25 +3326,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3427,25 +3427,25 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC29">
         <v>10</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE29">
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3528,25 +3528,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3629,25 +3629,25 @@
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD31">
         <v>5</v>
       </c>
       <c r="AE31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3730,25 +3730,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD32">
         <v>5</v>
       </c>
       <c r="AE32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3831,25 +3831,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD33">
         <v>5</v>
       </c>
       <c r="AE33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -3935,7 +3935,7 @@
         <v>10</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB34">
         <v>10</v>
@@ -3944,13 +3944,13 @@
         <v>10</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE34">
         <v>10</v>
       </c>
       <c r="AF34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG34">
         <v>10</v>
@@ -4033,25 +4033,25 @@
         <v>10</v>
       </c>
       <c r="Z35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE35">
         <v>10</v>
       </c>
       <c r="AF35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4137,22 +4137,22 @@
         <v>10</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC36">
         <v>10</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE36">
         <v>10</v>
       </c>
       <c r="AF36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG36">
         <v>10</v>
@@ -4238,16 +4238,16 @@
         <v>10</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC37">
         <v>10</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE37">
         <v>10</v>
@@ -4339,22 +4339,22 @@
         <v>10</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD38">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE38">
         <v>10</v>
       </c>
       <c r="AF38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG38">
         <v>10</v>
@@ -4440,22 +4440,22 @@
         <v>10</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE39">
         <v>10</v>
       </c>
       <c r="AF39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG39">
         <v>10</v>
@@ -4538,25 +4538,25 @@
         <v>10</v>
       </c>
       <c r="Z40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD40">
         <v>5</v>
       </c>
       <c r="AE40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG40">
         <v>10</v>
@@ -4639,7 +4639,7 @@
         <v>10</v>
       </c>
       <c r="Z41">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA41">
         <v>5</v>
@@ -4648,7 +4648,7 @@
         <v>5</v>
       </c>
       <c r="AC41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD41">
         <v>5</v>
@@ -4740,25 +4740,25 @@
         <v>10</v>
       </c>
       <c r="Z42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD42">
         <v>10</v>
       </c>
       <c r="AE42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG42">
         <v>10</v>
@@ -4841,25 +4841,25 @@
         <v>10</v>
       </c>
       <c r="Z43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB43">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC43">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE43">
         <v>10</v>
       </c>
       <c r="AF43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG43">
         <v>10</v>
@@ -8154,7 +8154,7 @@
         <v>25</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -8186,7 +8186,7 @@
         <v>10</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8218,7 +8218,7 @@
         <v>7.5</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8250,7 +8250,7 @@
         <v>7.5</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8282,7 +8282,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8346,7 +8346,7 @@
         <v>2.5</v>
       </c>
       <c r="H8">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8378,7 +8378,7 @@
         <v>2.5</v>
       </c>
       <c r="H9">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I9">
         <v>0</v>
